--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747522</v>
+        <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>92163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740920</v>
+        <v>740875</v>
       </c>
       <c r="R4" t="n">
-        <v>7126519</v>
+        <v>7126525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747527</v>
+        <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>91431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740608</v>
+        <v>740774</v>
       </c>
       <c r="R5" t="n">
-        <v>7126469</v>
+        <v>7126503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747520</v>
+        <v>128747522</v>
       </c>
       <c r="B6" t="n">
-        <v>92163</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740875</v>
+        <v>740920</v>
       </c>
       <c r="R6" t="n">
-        <v>7126525</v>
+        <v>7126519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747515</v>
+        <v>128747527</v>
       </c>
       <c r="B7" t="n">
-        <v>91431</v>
+        <v>57686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740774</v>
+        <v>740608</v>
       </c>
       <c r="R7" t="n">
-        <v>7126503</v>
+        <v>7126469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747537</v>
+        <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91484</v>
+        <v>91466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740896</v>
+        <v>740712</v>
       </c>
       <c r="R8" t="n">
-        <v>7126513</v>
+        <v>7126343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128747519</v>
+        <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91466</v>
+        <v>91484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740712</v>
+        <v>740896</v>
       </c>
       <c r="R9" t="n">
-        <v>7126343</v>
+        <v>7126513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128747518</v>
+        <v>128747525</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>57686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740764</v>
+        <v>740582</v>
       </c>
       <c r="R11" t="n">
-        <v>7126491</v>
+        <v>7126266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128747525</v>
+        <v>128747518</v>
       </c>
       <c r="B12" t="n">
-        <v>57686</v>
+        <v>79708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740582</v>
+        <v>740764</v>
       </c>
       <c r="R12" t="n">
-        <v>7126266</v>
+        <v>7126491</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747523</v>
+        <v>128747530</v>
       </c>
       <c r="B13" t="n">
-        <v>57686</v>
+        <v>80194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740707</v>
+        <v>740953</v>
       </c>
       <c r="R13" t="n">
-        <v>7126363</v>
+        <v>7126507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747530</v>
+        <v>128747523</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>57686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740953</v>
+        <v>740707</v>
       </c>
       <c r="R15" t="n">
-        <v>7126507</v>
+        <v>7126363</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747520</v>
+        <v>128747515</v>
       </c>
       <c r="B4" t="n">
-        <v>92163</v>
+        <v>91431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740875</v>
+        <v>740774</v>
       </c>
       <c r="R4" t="n">
-        <v>7126525</v>
+        <v>7126503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747515</v>
+        <v>128747522</v>
       </c>
       <c r="B5" t="n">
-        <v>91431</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740774</v>
+        <v>740920</v>
       </c>
       <c r="R5" t="n">
-        <v>7126503</v>
+        <v>7126519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747522</v>
+        <v>128747527</v>
       </c>
       <c r="B6" t="n">
         <v>57686</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740920</v>
+        <v>740608</v>
       </c>
       <c r="R6" t="n">
-        <v>7126519</v>
+        <v>7126469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747527</v>
+        <v>128747520</v>
       </c>
       <c r="B7" t="n">
-        <v>57686</v>
+        <v>92163</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740608</v>
+        <v>740875</v>
       </c>
       <c r="R7" t="n">
-        <v>7126469</v>
+        <v>7126525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128747525</v>
+        <v>128747518</v>
       </c>
       <c r="B11" t="n">
-        <v>57686</v>
+        <v>79708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740582</v>
+        <v>740764</v>
       </c>
       <c r="R11" t="n">
-        <v>7126266</v>
+        <v>7126491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128747518</v>
+        <v>128747525</v>
       </c>
       <c r="B12" t="n">
-        <v>79708</v>
+        <v>57686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740764</v>
+        <v>740582</v>
       </c>
       <c r="R12" t="n">
-        <v>7126491</v>
+        <v>7126266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747517</v>
+        <v>128747523</v>
       </c>
       <c r="B14" t="n">
-        <v>91431</v>
+        <v>57686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740633</v>
+        <v>740707</v>
       </c>
       <c r="R14" t="n">
-        <v>7126416</v>
+        <v>7126363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747523</v>
+        <v>128747517</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>91431</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740707</v>
+        <v>740633</v>
       </c>
       <c r="R15" t="n">
-        <v>7126363</v>
+        <v>7126416</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747515</v>
+        <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>91431</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740774</v>
+        <v>740875</v>
       </c>
       <c r="R4" t="n">
-        <v>7126503</v>
+        <v>7126525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747522</v>
+        <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>91432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740920</v>
+        <v>740774</v>
       </c>
       <c r="R5" t="n">
-        <v>7126519</v>
+        <v>7126503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747527</v>
+        <v>128747522</v>
       </c>
       <c r="B6" t="n">
         <v>57686</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740608</v>
+        <v>740920</v>
       </c>
       <c r="R6" t="n">
-        <v>7126469</v>
+        <v>7126519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747520</v>
+        <v>128747527</v>
       </c>
       <c r="B7" t="n">
-        <v>92163</v>
+        <v>57686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740875</v>
+        <v>740608</v>
       </c>
       <c r="R7" t="n">
-        <v>7126525</v>
+        <v>7126469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747530</v>
+        <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>80194</v>
+        <v>91432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740953</v>
+        <v>740633</v>
       </c>
       <c r="R13" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747517</v>
+        <v>128747530</v>
       </c>
       <c r="B15" t="n">
-        <v>91431</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740633</v>
+        <v>740953</v>
       </c>
       <c r="R15" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128747536</v>
       </c>
       <c r="B20" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128747540</v>
+        <v>128747529</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>97463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>740713</v>
+        <v>740710</v>
       </c>
       <c r="R23" t="n">
-        <v>7126372</v>
+        <v>7126339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128747529</v>
+        <v>128747540</v>
       </c>
       <c r="B24" t="n">
-        <v>97462</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740710</v>
+        <v>740713</v>
       </c>
       <c r="R24" t="n">
-        <v>7126339</v>
+        <v>7126372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128747542</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128747526</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747515</v>
+        <v>128747522</v>
       </c>
       <c r="B5" t="n">
-        <v>91432</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740774</v>
+        <v>740920</v>
       </c>
       <c r="R5" t="n">
-        <v>7126503</v>
+        <v>7126519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747522</v>
+        <v>128747527</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740920</v>
+        <v>740608</v>
       </c>
       <c r="R6" t="n">
-        <v>7126519</v>
+        <v>7126469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747527</v>
+        <v>128747515</v>
       </c>
       <c r="B7" t="n">
-        <v>57686</v>
+        <v>91459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740608</v>
+        <v>740774</v>
       </c>
       <c r="R7" t="n">
-        <v>7126469</v>
+        <v>7126503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128747521</v>
       </c>
       <c r="B10" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128747518</v>
+        <v>128747525</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>57713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740764</v>
+        <v>740582</v>
       </c>
       <c r="R11" t="n">
-        <v>7126491</v>
+        <v>7126266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128747525</v>
+        <v>128747518</v>
       </c>
       <c r="B12" t="n">
-        <v>57686</v>
+        <v>79735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740582</v>
+        <v>740764</v>
       </c>
       <c r="R12" t="n">
-        <v>7126266</v>
+        <v>7126491</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747523</v>
+        <v>128747530</v>
       </c>
       <c r="B14" t="n">
-        <v>57686</v>
+        <v>80221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740707</v>
+        <v>740953</v>
       </c>
       <c r="R14" t="n">
-        <v>7126363</v>
+        <v>7126507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747530</v>
+        <v>128747523</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>57713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740953</v>
+        <v>740707</v>
       </c>
       <c r="R15" t="n">
-        <v>7126507</v>
+        <v>7126363</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>128747543</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128747539</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128747531</v>
+        <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>80194</v>
+        <v>91512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>740934</v>
+        <v>740975</v>
       </c>
       <c r="R19" t="n">
-        <v>7126515</v>
+        <v>7126500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128747536</v>
+        <v>128747531</v>
       </c>
       <c r="B20" t="n">
-        <v>91485</v>
+        <v>80221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>740975</v>
+        <v>740934</v>
       </c>
       <c r="R20" t="n">
-        <v>7126500</v>
+        <v>7126515</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
         <v>128747538</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128747524</v>
       </c>
       <c r="B22" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128747529</v>
+        <v>128747540</v>
       </c>
       <c r="B23" t="n">
-        <v>97463</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>740710</v>
+        <v>740713</v>
       </c>
       <c r="R23" t="n">
-        <v>7126339</v>
+        <v>7126372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128747540</v>
+        <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>97490</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740713</v>
+        <v>740710</v>
       </c>
       <c r="R24" t="n">
-        <v>7126372</v>
+        <v>7126339</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747542</v>
+        <v>128747526</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740608</v>
+        <v>740633</v>
       </c>
       <c r="R2" t="n">
-        <v>7126431</v>
+        <v>7126416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747526</v>
+        <v>128747542</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740633</v>
+        <v>740608</v>
       </c>
       <c r="R3" t="n">
-        <v>7126416</v>
+        <v>7126431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747517</v>
+        <v>128747530</v>
       </c>
       <c r="B13" t="n">
-        <v>91459</v>
+        <v>80221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740633</v>
+        <v>740953</v>
       </c>
       <c r="R13" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747530</v>
+        <v>128747523</v>
       </c>
       <c r="B14" t="n">
-        <v>80221</v>
+        <v>57713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740953</v>
+        <v>740707</v>
       </c>
       <c r="R14" t="n">
-        <v>7126507</v>
+        <v>7126363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747523</v>
+        <v>128747517</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>91459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740707</v>
+        <v>740633</v>
       </c>
       <c r="R15" t="n">
-        <v>7126363</v>
+        <v>7126416</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128747540</v>
+        <v>128747529</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>97490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>740713</v>
+        <v>740710</v>
       </c>
       <c r="R23" t="n">
-        <v>7126372</v>
+        <v>7126339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128747529</v>
+        <v>128747540</v>
       </c>
       <c r="B24" t="n">
-        <v>97490</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740710</v>
+        <v>740713</v>
       </c>
       <c r="R24" t="n">
-        <v>7126339</v>
+        <v>7126372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128747542</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747522</v>
+        <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>91464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740920</v>
+        <v>740774</v>
       </c>
       <c r="R5" t="n">
-        <v>7126519</v>
+        <v>7126503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747527</v>
+        <v>128747522</v>
       </c>
       <c r="B6" t="n">
         <v>57713</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740608</v>
+        <v>740920</v>
       </c>
       <c r="R6" t="n">
-        <v>7126469</v>
+        <v>7126519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747515</v>
+        <v>128747527</v>
       </c>
       <c r="B7" t="n">
-        <v>91459</v>
+        <v>57713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740774</v>
+        <v>740608</v>
       </c>
       <c r="R7" t="n">
-        <v>7126503</v>
+        <v>7126469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747519</v>
+        <v>128747537</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>91517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740712</v>
+        <v>740896</v>
       </c>
       <c r="R8" t="n">
-        <v>7126343</v>
+        <v>7126513</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128747537</v>
+        <v>128747519</v>
       </c>
       <c r="B9" t="n">
-        <v>91512</v>
+        <v>91499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740896</v>
+        <v>740712</v>
       </c>
       <c r="R9" t="n">
-        <v>7126513</v>
+        <v>7126343</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128747518</v>
       </c>
       <c r="B12" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128747530</v>
       </c>
       <c r="B13" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747523</v>
+        <v>128747517</v>
       </c>
       <c r="B14" t="n">
-        <v>57713</v>
+        <v>91464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740707</v>
+        <v>740633</v>
       </c>
       <c r="R14" t="n">
-        <v>7126363</v>
+        <v>7126416</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747517</v>
+        <v>128747523</v>
       </c>
       <c r="B15" t="n">
-        <v>91459</v>
+        <v>57713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740633</v>
+        <v>740707</v>
       </c>
       <c r="R15" t="n">
-        <v>7126416</v>
+        <v>7126363</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>128747543</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128747539</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128747531</v>
       </c>
       <c r="B20" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128747538</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128747529</v>
+        <v>128747540</v>
       </c>
       <c r="B23" t="n">
-        <v>97490</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>740710</v>
+        <v>740713</v>
       </c>
       <c r="R23" t="n">
-        <v>7126339</v>
+        <v>7126372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128747540</v>
+        <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>97496</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740713</v>
+        <v>740710</v>
       </c>
       <c r="R24" t="n">
-        <v>7126372</v>
+        <v>7126339</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747526</v>
+        <v>128747542</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740633</v>
+        <v>740608</v>
       </c>
       <c r="R2" t="n">
-        <v>7126416</v>
+        <v>7126431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747542</v>
+        <v>128747526</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740608</v>
+        <v>740633</v>
       </c>
       <c r="R3" t="n">
-        <v>7126431</v>
+        <v>7126416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128747537</v>
       </c>
       <c r="B8" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747519</v>
       </c>
       <c r="B9" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128747525</v>
+        <v>128747518</v>
       </c>
       <c r="B11" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740582</v>
+        <v>740764</v>
       </c>
       <c r="R11" t="n">
-        <v>7126266</v>
+        <v>7126491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128747518</v>
+        <v>128747525</v>
       </c>
       <c r="B12" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740764</v>
+        <v>740582</v>
       </c>
       <c r="R12" t="n">
-        <v>7126491</v>
+        <v>7126266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747530</v>
+        <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>80225</v>
+        <v>91469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740953</v>
+        <v>740633</v>
       </c>
       <c r="R13" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747517</v>
+        <v>128747530</v>
       </c>
       <c r="B14" t="n">
-        <v>91464</v>
+        <v>80225</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740633</v>
+        <v>740953</v>
       </c>
       <c r="R14" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747520</v>
+        <v>128747515</v>
       </c>
       <c r="B4" t="n">
-        <v>92201</v>
+        <v>91469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740875</v>
+        <v>740774</v>
       </c>
       <c r="R4" t="n">
-        <v>7126525</v>
+        <v>7126503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747515</v>
+        <v>128747520</v>
       </c>
       <c r="B5" t="n">
-        <v>91469</v>
+        <v>92201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740774</v>
+        <v>740875</v>
       </c>
       <c r="R5" t="n">
-        <v>7126503</v>
+        <v>7126525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747537</v>
+        <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740896</v>
+        <v>740712</v>
       </c>
       <c r="R8" t="n">
-        <v>7126513</v>
+        <v>7126343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128747519</v>
+        <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740712</v>
+        <v>740896</v>
       </c>
       <c r="R9" t="n">
-        <v>7126343</v>
+        <v>7126513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747517</v>
+        <v>128747523</v>
       </c>
       <c r="B13" t="n">
-        <v>91469</v>
+        <v>57713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740633</v>
+        <v>740707</v>
       </c>
       <c r="R13" t="n">
-        <v>7126416</v>
+        <v>7126363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747523</v>
+        <v>128747517</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>91469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740707</v>
+        <v>740633</v>
       </c>
       <c r="R15" t="n">
-        <v>7126363</v>
+        <v>7126416</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128747536</v>
+        <v>128747531</v>
       </c>
       <c r="B19" t="n">
-        <v>91522</v>
+        <v>80225</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>740975</v>
+        <v>740934</v>
       </c>
       <c r="R19" t="n">
-        <v>7126500</v>
+        <v>7126515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128747531</v>
+        <v>128747536</v>
       </c>
       <c r="B20" t="n">
-        <v>80225</v>
+        <v>91522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>740934</v>
+        <v>740975</v>
       </c>
       <c r="R20" t="n">
-        <v>7126515</v>
+        <v>7126500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747515</v>
+        <v>128747522</v>
       </c>
       <c r="B4" t="n">
-        <v>91469</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740774</v>
+        <v>740920</v>
       </c>
       <c r="R4" t="n">
-        <v>7126503</v>
+        <v>7126519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747520</v>
+        <v>128747527</v>
       </c>
       <c r="B5" t="n">
-        <v>92201</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740875</v>
+        <v>740608</v>
       </c>
       <c r="R5" t="n">
-        <v>7126525</v>
+        <v>7126469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747522</v>
+        <v>128747520</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>92201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740920</v>
+        <v>740875</v>
       </c>
       <c r="R6" t="n">
-        <v>7126519</v>
+        <v>7126525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747527</v>
+        <v>128747515</v>
       </c>
       <c r="B7" t="n">
-        <v>57713</v>
+        <v>91469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740608</v>
+        <v>740774</v>
       </c>
       <c r="R7" t="n">
-        <v>7126469</v>
+        <v>7126503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747519</v>
+        <v>128747537</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740712</v>
+        <v>740896</v>
       </c>
       <c r="R8" t="n">
-        <v>7126343</v>
+        <v>7126513</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128747537</v>
+        <v>128747519</v>
       </c>
       <c r="B9" t="n">
-        <v>91522</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740896</v>
+        <v>740712</v>
       </c>
       <c r="R9" t="n">
-        <v>7126513</v>
+        <v>7126343</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747530</v>
+        <v>128747517</v>
       </c>
       <c r="B14" t="n">
-        <v>80225</v>
+        <v>91469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740953</v>
+        <v>740633</v>
       </c>
       <c r="R14" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747517</v>
+        <v>128747530</v>
       </c>
       <c r="B15" t="n">
-        <v>91469</v>
+        <v>80225</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740633</v>
+        <v>740953</v>
       </c>
       <c r="R15" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128747542</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128747526</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747522</v>
+        <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>92205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740920</v>
+        <v>740875</v>
       </c>
       <c r="R4" t="n">
-        <v>7126519</v>
+        <v>7126525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747527</v>
+        <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>91473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740608</v>
+        <v>740774</v>
       </c>
       <c r="R5" t="n">
-        <v>7126469</v>
+        <v>7126503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747520</v>
+        <v>128747522</v>
       </c>
       <c r="B6" t="n">
-        <v>92201</v>
+        <v>57717</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740875</v>
+        <v>740920</v>
       </c>
       <c r="R6" t="n">
-        <v>7126525</v>
+        <v>7126519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747515</v>
+        <v>128747527</v>
       </c>
       <c r="B7" t="n">
-        <v>91469</v>
+        <v>57717</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740774</v>
+        <v>740608</v>
       </c>
       <c r="R7" t="n">
-        <v>7126503</v>
+        <v>7126469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747537</v>
+        <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>91508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740896</v>
+        <v>740712</v>
       </c>
       <c r="R8" t="n">
-        <v>7126513</v>
+        <v>7126343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128747519</v>
+        <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740712</v>
+        <v>740896</v>
       </c>
       <c r="R9" t="n">
-        <v>7126343</v>
+        <v>7126513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>128747521</v>
       </c>
       <c r="B10" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128747518</v>
       </c>
       <c r="B11" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128747525</v>
       </c>
       <c r="B12" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128747523</v>
       </c>
       <c r="B13" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128747517</v>
       </c>
       <c r="B14" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128747530</v>
       </c>
       <c r="B15" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128747543</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128747539</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128747531</v>
+        <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>80225</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>740934</v>
+        <v>740975</v>
       </c>
       <c r="R19" t="n">
-        <v>7126515</v>
+        <v>7126500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128747536</v>
+        <v>128747531</v>
       </c>
       <c r="B20" t="n">
-        <v>91522</v>
+        <v>80229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>740975</v>
+        <v>740934</v>
       </c>
       <c r="R20" t="n">
-        <v>7126500</v>
+        <v>7126515</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
         <v>128747538</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128747524</v>
       </c>
       <c r="B22" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128747540</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747523</v>
+        <v>128747530</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>80229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740707</v>
+        <v>740953</v>
       </c>
       <c r="R13" t="n">
-        <v>7126363</v>
+        <v>7126507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747530</v>
+        <v>128747523</v>
       </c>
       <c r="B15" t="n">
-        <v>80229</v>
+        <v>57717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740953</v>
+        <v>740707</v>
       </c>
       <c r="R15" t="n">
-        <v>7126507</v>
+        <v>7126363</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128747536</v>
+        <v>128747531</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>80229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>740975</v>
+        <v>740934</v>
       </c>
       <c r="R19" t="n">
-        <v>7126500</v>
+        <v>7126515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128747531</v>
+        <v>128747536</v>
       </c>
       <c r="B20" t="n">
-        <v>80229</v>
+        <v>91526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>740934</v>
+        <v>740975</v>
       </c>
       <c r="R20" t="n">
-        <v>7126515</v>
+        <v>7126500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747520</v>
+        <v>128747515</v>
       </c>
       <c r="B4" t="n">
-        <v>92205</v>
+        <v>91473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740875</v>
+        <v>740774</v>
       </c>
       <c r="R4" t="n">
-        <v>7126525</v>
+        <v>7126503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747515</v>
+        <v>128747522</v>
       </c>
       <c r="B5" t="n">
-        <v>91473</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740774</v>
+        <v>740920</v>
       </c>
       <c r="R5" t="n">
-        <v>7126503</v>
+        <v>7126519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747522</v>
+        <v>128747527</v>
       </c>
       <c r="B6" t="n">
         <v>57717</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740920</v>
+        <v>740608</v>
       </c>
       <c r="R6" t="n">
-        <v>7126519</v>
+        <v>7126469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747527</v>
+        <v>128747520</v>
       </c>
       <c r="B7" t="n">
-        <v>57717</v>
+        <v>92205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740608</v>
+        <v>740875</v>
       </c>
       <c r="R7" t="n">
-        <v>7126469</v>
+        <v>7126525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747519</v>
+        <v>128747537</v>
       </c>
       <c r="B8" t="n">
-        <v>91508</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740712</v>
+        <v>740896</v>
       </c>
       <c r="R8" t="n">
-        <v>7126343</v>
+        <v>7126513</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128747537</v>
+        <v>128747519</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740896</v>
+        <v>740712</v>
       </c>
       <c r="R9" t="n">
-        <v>7126513</v>
+        <v>7126343</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747530</v>
+        <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>80229</v>
+        <v>91473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740953</v>
+        <v>740633</v>
       </c>
       <c r="R13" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747517</v>
+        <v>128747530</v>
       </c>
       <c r="B14" t="n">
-        <v>91473</v>
+        <v>80229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740633</v>
+        <v>740953</v>
       </c>
       <c r="R14" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128747531</v>
+        <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>80229</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>740934</v>
+        <v>740975</v>
       </c>
       <c r="R19" t="n">
-        <v>7126515</v>
+        <v>7126500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128747536</v>
+        <v>128747531</v>
       </c>
       <c r="B20" t="n">
-        <v>91526</v>
+        <v>80229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>740975</v>
+        <v>740934</v>
       </c>
       <c r="R20" t="n">
-        <v>7126500</v>
+        <v>7126515</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128747542</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128747526</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747515</v>
+        <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>91473</v>
+        <v>92210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740774</v>
+        <v>740875</v>
       </c>
       <c r="R4" t="n">
-        <v>7126503</v>
+        <v>7126525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747522</v>
+        <v>128747527</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740920</v>
+        <v>740608</v>
       </c>
       <c r="R5" t="n">
-        <v>7126519</v>
+        <v>7126469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747527</v>
+        <v>128747522</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740608</v>
+        <v>740920</v>
       </c>
       <c r="R6" t="n">
-        <v>7126469</v>
+        <v>7126519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747520</v>
+        <v>128747515</v>
       </c>
       <c r="B7" t="n">
-        <v>92205</v>
+        <v>91478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740875</v>
+        <v>740774</v>
       </c>
       <c r="R7" t="n">
-        <v>7126525</v>
+        <v>7126503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128747537</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747519</v>
       </c>
       <c r="B9" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128747521</v>
       </c>
       <c r="B10" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128747518</v>
+        <v>128747525</v>
       </c>
       <c r="B11" t="n">
-        <v>79743</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740764</v>
+        <v>740582</v>
       </c>
       <c r="R11" t="n">
-        <v>7126491</v>
+        <v>7126266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128747525</v>
+        <v>128747518</v>
       </c>
       <c r="B12" t="n">
-        <v>57717</v>
+        <v>79648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740582</v>
+        <v>740764</v>
       </c>
       <c r="R12" t="n">
-        <v>7126266</v>
+        <v>7126491</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747530</v>
+        <v>128747523</v>
       </c>
       <c r="B14" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740953</v>
+        <v>740707</v>
       </c>
       <c r="R14" t="n">
-        <v>7126507</v>
+        <v>7126363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747523</v>
+        <v>128747530</v>
       </c>
       <c r="B15" t="n">
-        <v>57717</v>
+        <v>80134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740707</v>
+        <v>740953</v>
       </c>
       <c r="R15" t="n">
-        <v>7126363</v>
+        <v>7126507</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>128747543</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128747539</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128747531</v>
       </c>
       <c r="B20" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128747538</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128747524</v>
       </c>
       <c r="B22" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128747540</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747522</v>
+        <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>91488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740920</v>
+        <v>740774</v>
       </c>
       <c r="R5" t="n">
-        <v>7126519</v>
+        <v>7126503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747527</v>
+        <v>128747522</v>
       </c>
       <c r="B6" t="n">
         <v>57720</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740608</v>
+        <v>740920</v>
       </c>
       <c r="R6" t="n">
-        <v>7126469</v>
+        <v>7126519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747515</v>
+        <v>128747527</v>
       </c>
       <c r="B7" t="n">
-        <v>91485</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740774</v>
+        <v>740608</v>
       </c>
       <c r="R7" t="n">
-        <v>7126503</v>
+        <v>7126469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747517</v>
+        <v>128747530</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>80139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740633</v>
+        <v>740953</v>
       </c>
       <c r="R13" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747530</v>
+        <v>128747517</v>
       </c>
       <c r="B15" t="n">
-        <v>80139</v>
+        <v>91488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740953</v>
+        <v>740633</v>
       </c>
       <c r="R15" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128747540</v>
+        <v>128747529</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>97527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>740713</v>
+        <v>740710</v>
       </c>
       <c r="R23" t="n">
-        <v>7126372</v>
+        <v>7126339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128747529</v>
+        <v>128747540</v>
       </c>
       <c r="B24" t="n">
-        <v>97522</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740710</v>
+        <v>740713</v>
       </c>
       <c r="R24" t="n">
-        <v>7126339</v>
+        <v>7126372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128747542</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128747518</v>
       </c>
       <c r="B11" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128747530</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128747517</v>
       </c>
       <c r="B15" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128747543</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128747539</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128747531</v>
       </c>
       <c r="B20" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128747538</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128747529</v>
+        <v>128747540</v>
       </c>
       <c r="B23" t="n">
-        <v>97527</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>740710</v>
+        <v>740713</v>
       </c>
       <c r="R23" t="n">
-        <v>7126339</v>
+        <v>7126372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128747540</v>
+        <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>97530</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740713</v>
+        <v>740710</v>
       </c>
       <c r="R24" t="n">
-        <v>7126372</v>
+        <v>7126339</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747530</v>
+        <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>91491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740953</v>
+        <v>740633</v>
       </c>
       <c r="R13" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747523</v>
+        <v>128747530</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740707</v>
+        <v>740953</v>
       </c>
       <c r="R14" t="n">
-        <v>7126363</v>
+        <v>7126507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747517</v>
+        <v>128747523</v>
       </c>
       <c r="B15" t="n">
-        <v>91491</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740633</v>
+        <v>740707</v>
       </c>
       <c r="R15" t="n">
-        <v>7126416</v>
+        <v>7126363</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747520</v>
+        <v>128747515</v>
       </c>
       <c r="B4" t="n">
-        <v>92226</v>
+        <v>91491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740875</v>
+        <v>740774</v>
       </c>
       <c r="R4" t="n">
-        <v>7126525</v>
+        <v>7126503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747515</v>
+        <v>128747522</v>
       </c>
       <c r="B5" t="n">
-        <v>91491</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740774</v>
+        <v>740920</v>
       </c>
       <c r="R5" t="n">
-        <v>7126503</v>
+        <v>7126519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747522</v>
+        <v>128747527</v>
       </c>
       <c r="B6" t="n">
         <v>57720</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740920</v>
+        <v>740608</v>
       </c>
       <c r="R6" t="n">
-        <v>7126519</v>
+        <v>7126469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747527</v>
+        <v>128747520</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>92226</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740608</v>
+        <v>740875</v>
       </c>
       <c r="R7" t="n">
-        <v>7126469</v>
+        <v>7126525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747519</v>
+        <v>128747537</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91544</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740712</v>
+        <v>740896</v>
       </c>
       <c r="R8" t="n">
-        <v>7126343</v>
+        <v>7126513</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128747537</v>
+        <v>128747519</v>
       </c>
       <c r="B9" t="n">
-        <v>91544</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740896</v>
+        <v>740712</v>
       </c>
       <c r="R9" t="n">
-        <v>7126513</v>
+        <v>7126343</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747517</v>
+        <v>128747530</v>
       </c>
       <c r="B13" t="n">
-        <v>91491</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740633</v>
+        <v>740953</v>
       </c>
       <c r="R13" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747530</v>
+        <v>128747517</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>91491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740953</v>
+        <v>740633</v>
       </c>
       <c r="R14" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747542</v>
+        <v>128747526</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740608</v>
+        <v>740633</v>
       </c>
       <c r="R2" t="n">
-        <v>7126431</v>
+        <v>7126416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747526</v>
+        <v>128747542</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740633</v>
+        <v>740608</v>
       </c>
       <c r="R3" t="n">
-        <v>7126416</v>
+        <v>7126431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128747515</v>
       </c>
       <c r="B4" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747522</v>
+        <v>128747520</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>92233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740920</v>
+        <v>740875</v>
       </c>
       <c r="R5" t="n">
-        <v>7126519</v>
+        <v>7126525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747527</v>
+        <v>128747522</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740608</v>
+        <v>740920</v>
       </c>
       <c r="R6" t="n">
-        <v>7126469</v>
+        <v>7126519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747520</v>
+        <v>128747527</v>
       </c>
       <c r="B7" t="n">
-        <v>92226</v>
+        <v>57722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740875</v>
+        <v>740608</v>
       </c>
       <c r="R7" t="n">
-        <v>7126525</v>
+        <v>7126469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128747537</v>
       </c>
       <c r="B8" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747519</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128747521</v>
       </c>
       <c r="B10" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128747518</v>
       </c>
       <c r="B11" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128747525</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128747530</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128747517</v>
       </c>
       <c r="B14" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128747523</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128747543</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128747539</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128747531</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128747538</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128747524</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128747540</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747515</v>
+        <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>91497</v>
+        <v>92233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740774</v>
+        <v>740875</v>
       </c>
       <c r="R4" t="n">
-        <v>7126503</v>
+        <v>7126525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747520</v>
+        <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>91497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740875</v>
+        <v>740774</v>
       </c>
       <c r="R5" t="n">
-        <v>7126525</v>
+        <v>7126503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128747518</v>
+        <v>128747525</v>
       </c>
       <c r="B11" t="n">
-        <v>79658</v>
+        <v>57722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740764</v>
+        <v>740582</v>
       </c>
       <c r="R11" t="n">
-        <v>7126491</v>
+        <v>7126266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128747525</v>
+        <v>128747518</v>
       </c>
       <c r="B12" t="n">
-        <v>57722</v>
+        <v>79658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740582</v>
+        <v>740764</v>
       </c>
       <c r="R12" t="n">
-        <v>7126266</v>
+        <v>7126491</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747517</v>
+        <v>128747523</v>
       </c>
       <c r="B14" t="n">
-        <v>91497</v>
+        <v>57722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740633</v>
+        <v>740707</v>
       </c>
       <c r="R14" t="n">
-        <v>7126416</v>
+        <v>7126363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747523</v>
+        <v>128747517</v>
       </c>
       <c r="B15" t="n">
-        <v>57722</v>
+        <v>91497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740707</v>
+        <v>740633</v>
       </c>
       <c r="R15" t="n">
-        <v>7126363</v>
+        <v>7126416</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128747540</v>
+        <v>128747529</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>97540</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>740713</v>
+        <v>740710</v>
       </c>
       <c r="R23" t="n">
-        <v>7126372</v>
+        <v>7126339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128747529</v>
+        <v>128747540</v>
       </c>
       <c r="B24" t="n">
-        <v>97540</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740710</v>
+        <v>740713</v>
       </c>
       <c r="R24" t="n">
-        <v>7126339</v>
+        <v>7126372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747526</v>
+        <v>128747542</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740633</v>
+        <v>740608</v>
       </c>
       <c r="R2" t="n">
-        <v>7126416</v>
+        <v>7126431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747542</v>
+        <v>128747526</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740608</v>
+        <v>740633</v>
       </c>
       <c r="R3" t="n">
-        <v>7126431</v>
+        <v>7126416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747537</v>
+        <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91551</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740896</v>
+        <v>740712</v>
       </c>
       <c r="R8" t="n">
-        <v>7126513</v>
+        <v>7126343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128747519</v>
+        <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740712</v>
+        <v>740896</v>
       </c>
       <c r="R9" t="n">
-        <v>7126343</v>
+        <v>7126513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128747525</v>
+        <v>128747518</v>
       </c>
       <c r="B11" t="n">
-        <v>57722</v>
+        <v>79658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740582</v>
+        <v>740764</v>
       </c>
       <c r="R11" t="n">
-        <v>7126266</v>
+        <v>7126491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128747518</v>
+        <v>128747525</v>
       </c>
       <c r="B12" t="n">
-        <v>79658</v>
+        <v>57722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740764</v>
+        <v>740582</v>
       </c>
       <c r="R12" t="n">
-        <v>7126491</v>
+        <v>7126266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747530</v>
+        <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740953</v>
+        <v>740633</v>
       </c>
       <c r="R13" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747517</v>
+        <v>128747530</v>
       </c>
       <c r="B15" t="n">
-        <v>91497</v>
+        <v>80144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740633</v>
+        <v>740953</v>
       </c>
       <c r="R15" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128747536</v>
+        <v>128747531</v>
       </c>
       <c r="B19" t="n">
-        <v>91551</v>
+        <v>80144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>740975</v>
+        <v>740934</v>
       </c>
       <c r="R19" t="n">
-        <v>7126500</v>
+        <v>7126515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128747531</v>
+        <v>128747536</v>
       </c>
       <c r="B20" t="n">
-        <v>80144</v>
+        <v>91558</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>740934</v>
+        <v>740975</v>
       </c>
       <c r="R20" t="n">
-        <v>7126515</v>
+        <v>7126500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128747529</v>
+        <v>128747540</v>
       </c>
       <c r="B23" t="n">
-        <v>97540</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>740710</v>
+        <v>740713</v>
       </c>
       <c r="R23" t="n">
-        <v>7126339</v>
+        <v>7126372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128747540</v>
+        <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>97547</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740713</v>
+        <v>740710</v>
       </c>
       <c r="R24" t="n">
-        <v>7126372</v>
+        <v>7126339</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747542</v>
+        <v>128747526</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740608</v>
+        <v>740633</v>
       </c>
       <c r="R2" t="n">
-        <v>7126431</v>
+        <v>7126416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747526</v>
+        <v>128747542</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740633</v>
+        <v>740608</v>
       </c>
       <c r="R3" t="n">
-        <v>7126416</v>
+        <v>7126431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747520</v>
+        <v>128747522</v>
       </c>
       <c r="B4" t="n">
-        <v>92240</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740875</v>
+        <v>740920</v>
       </c>
       <c r="R4" t="n">
-        <v>7126525</v>
+        <v>7126519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747515</v>
+        <v>128747527</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740774</v>
+        <v>740608</v>
       </c>
       <c r="R5" t="n">
-        <v>7126503</v>
+        <v>7126469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747522</v>
+        <v>128747520</v>
       </c>
       <c r="B6" t="n">
-        <v>57722</v>
+        <v>92242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740920</v>
+        <v>740875</v>
       </c>
       <c r="R6" t="n">
-        <v>7126519</v>
+        <v>7126525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747527</v>
+        <v>128747515</v>
       </c>
       <c r="B7" t="n">
-        <v>57722</v>
+        <v>91506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740608</v>
+        <v>740774</v>
       </c>
       <c r="R7" t="n">
-        <v>7126469</v>
+        <v>7126503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128747521</v>
       </c>
       <c r="B10" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128747518</v>
+        <v>128747525</v>
       </c>
       <c r="B11" t="n">
-        <v>79658</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740764</v>
+        <v>740582</v>
       </c>
       <c r="R11" t="n">
-        <v>7126491</v>
+        <v>7126266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128747525</v>
+        <v>128747518</v>
       </c>
       <c r="B12" t="n">
-        <v>57722</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740582</v>
+        <v>740764</v>
       </c>
       <c r="R12" t="n">
-        <v>7126266</v>
+        <v>7126491</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128747523</v>
       </c>
       <c r="B14" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128747530</v>
       </c>
       <c r="B15" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128747543</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128747539</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128747531</v>
+        <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>80144</v>
+        <v>91560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>740934</v>
+        <v>740975</v>
       </c>
       <c r="R19" t="n">
-        <v>7126515</v>
+        <v>7126500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128747536</v>
+        <v>128747531</v>
       </c>
       <c r="B20" t="n">
-        <v>91558</v>
+        <v>80146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>740975</v>
+        <v>740934</v>
       </c>
       <c r="R20" t="n">
-        <v>7126500</v>
+        <v>7126515</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
         <v>128747538</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128747524</v>
       </c>
       <c r="B22" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128747540</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747526</v>
+        <v>128747542</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740633</v>
+        <v>740608</v>
       </c>
       <c r="R2" t="n">
-        <v>7126416</v>
+        <v>7126431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747542</v>
+        <v>128747526</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740608</v>
+        <v>740633</v>
       </c>
       <c r="R3" t="n">
-        <v>7126431</v>
+        <v>7126416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747522</v>
+        <v>128747515</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>91506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740920</v>
+        <v>740774</v>
       </c>
       <c r="R4" t="n">
-        <v>7126519</v>
+        <v>7126503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747520</v>
+        <v>128747522</v>
       </c>
       <c r="B6" t="n">
-        <v>92242</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740875</v>
+        <v>740920</v>
       </c>
       <c r="R6" t="n">
-        <v>7126525</v>
+        <v>7126519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747515</v>
+        <v>128747520</v>
       </c>
       <c r="B7" t="n">
-        <v>91506</v>
+        <v>92242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740774</v>
+        <v>740875</v>
       </c>
       <c r="R7" t="n">
-        <v>7126503</v>
+        <v>7126525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747519</v>
+        <v>128747537</v>
       </c>
       <c r="B8" t="n">
-        <v>91542</v>
+        <v>91560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740712</v>
+        <v>740896</v>
       </c>
       <c r="R8" t="n">
-        <v>7126343</v>
+        <v>7126513</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128747537</v>
+        <v>128747519</v>
       </c>
       <c r="B9" t="n">
-        <v>91560</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740896</v>
+        <v>740712</v>
       </c>
       <c r="R9" t="n">
-        <v>7126513</v>
+        <v>7126343</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747517</v>
+        <v>128747523</v>
       </c>
       <c r="B13" t="n">
-        <v>91506</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740633</v>
+        <v>740707</v>
       </c>
       <c r="R13" t="n">
-        <v>7126416</v>
+        <v>7126363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747523</v>
+        <v>128747530</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740707</v>
+        <v>740953</v>
       </c>
       <c r="R14" t="n">
-        <v>7126363</v>
+        <v>7126507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747530</v>
+        <v>128747517</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>91506</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740953</v>
+        <v>740633</v>
       </c>
       <c r="R15" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747542</v>
+        <v>128747526</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740608</v>
+        <v>740633</v>
       </c>
       <c r="R2" t="n">
-        <v>7126431</v>
+        <v>7126416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747526</v>
+        <v>128747542</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740633</v>
+        <v>740608</v>
       </c>
       <c r="R3" t="n">
-        <v>7126416</v>
+        <v>7126431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747537</v>
+        <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91560</v>
+        <v>91542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740896</v>
+        <v>740712</v>
       </c>
       <c r="R8" t="n">
-        <v>7126513</v>
+        <v>7126343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128747519</v>
+        <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740712</v>
+        <v>740896</v>
       </c>
       <c r="R9" t="n">
-        <v>7126343</v>
+        <v>7126513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747526</v>
+        <v>128747542</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740633</v>
+        <v>740608</v>
       </c>
       <c r="R2" t="n">
-        <v>7126416</v>
+        <v>7126431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747542</v>
+        <v>128747526</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740608</v>
+        <v>740633</v>
       </c>
       <c r="R3" t="n">
-        <v>7126431</v>
+        <v>7126416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747515</v>
+        <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>91506</v>
+        <v>92257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740774</v>
+        <v>740875</v>
       </c>
       <c r="R4" t="n">
-        <v>7126503</v>
+        <v>7126525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747527</v>
+        <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740608</v>
+        <v>740774</v>
       </c>
       <c r="R5" t="n">
-        <v>7126469</v>
+        <v>7126503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747522</v>
+        <v>128747527</v>
       </c>
       <c r="B6" t="n">
         <v>57724</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740920</v>
+        <v>740608</v>
       </c>
       <c r="R6" t="n">
-        <v>7126519</v>
+        <v>7126469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747520</v>
+        <v>128747522</v>
       </c>
       <c r="B7" t="n">
-        <v>92242</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740875</v>
+        <v>740920</v>
       </c>
       <c r="R7" t="n">
-        <v>7126525</v>
+        <v>7126519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128747525</v>
+        <v>128747518</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740582</v>
+        <v>740764</v>
       </c>
       <c r="R11" t="n">
-        <v>7126266</v>
+        <v>7126491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128747518</v>
+        <v>128747525</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740764</v>
+        <v>740582</v>
       </c>
       <c r="R12" t="n">
-        <v>7126491</v>
+        <v>7126266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747523</v>
+        <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740707</v>
+        <v>740633</v>
       </c>
       <c r="R13" t="n">
-        <v>7126363</v>
+        <v>7126416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128747517</v>
+        <v>128747523</v>
       </c>
       <c r="B15" t="n">
-        <v>91506</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740633</v>
+        <v>740707</v>
       </c>
       <c r="R15" t="n">
-        <v>7126416</v>
+        <v>7126363</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747542</v>
+        <v>128747526</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740608</v>
+        <v>740633</v>
       </c>
       <c r="R2" t="n">
-        <v>7126431</v>
+        <v>7126416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747526</v>
+        <v>128747542</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740633</v>
+        <v>740608</v>
       </c>
       <c r="R3" t="n">
-        <v>7126416</v>
+        <v>7126431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747520</v>
+        <v>128747527</v>
       </c>
       <c r="B4" t="n">
-        <v>92257</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740875</v>
+        <v>740608</v>
       </c>
       <c r="R4" t="n">
-        <v>7126525</v>
+        <v>7126469</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747515</v>
+        <v>128747520</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>92258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740774</v>
+        <v>740875</v>
       </c>
       <c r="R5" t="n">
-        <v>7126503</v>
+        <v>7126525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747527</v>
+        <v>128747515</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740608</v>
+        <v>740774</v>
       </c>
       <c r="R6" t="n">
-        <v>7126469</v>
+        <v>7126503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,14 +1374,10 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1742,32 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747517</v>
+        <v>128747530</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740633</v>
+        <v>740953</v>
       </c>
       <c r="R13" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1835,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747530</v>
+        <v>128747517</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>91504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740953</v>
+        <v>740633</v>
       </c>
       <c r="R14" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2324,10 +2320,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128747536</v>
+        <v>128747531</v>
       </c>
       <c r="B19" t="n">
-        <v>91558</v>
+        <v>80146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2331,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2355,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>740975</v>
+        <v>740934</v>
       </c>
       <c r="R19" t="n">
-        <v>7126500</v>
+        <v>7126515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2417,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128747531</v>
+        <v>128747536</v>
       </c>
       <c r="B20" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,23 +2428,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2456,10 +2448,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>740934</v>
+        <v>740975</v>
       </c>
       <c r="R20" t="n">
-        <v>7126515</v>
+        <v>7126500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,32 +2704,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128747540</v>
+        <v>128747529</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>97576</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2739,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>740713</v>
+        <v>740710</v>
       </c>
       <c r="R23" t="n">
-        <v>7126372</v>
+        <v>7126339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2801,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128747529</v>
+        <v>128747540</v>
       </c>
       <c r="B24" t="n">
-        <v>97575</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2836,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740710</v>
+        <v>740713</v>
       </c>
       <c r="R24" t="n">
-        <v>7126339</v>
+        <v>7126372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747527</v>
+        <v>128747515</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740608</v>
+        <v>740774</v>
       </c>
       <c r="R4" t="n">
-        <v>7126469</v>
+        <v>7126503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747515</v>
+        <v>128747522</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740774</v>
+        <v>740920</v>
       </c>
       <c r="R6" t="n">
-        <v>7126503</v>
+        <v>7126519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747522</v>
+        <v>128747527</v>
       </c>
       <c r="B7" t="n">
         <v>57724</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740920</v>
+        <v>740608</v>
       </c>
       <c r="R7" t="n">
-        <v>7126519</v>
+        <v>7126469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1738,32 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128747530</v>
+        <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740953</v>
+        <v>740633</v>
       </c>
       <c r="R13" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1835,32 +1835,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128747517</v>
+        <v>128747530</v>
       </c>
       <c r="B14" t="n">
-        <v>91504</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740633</v>
+        <v>740953</v>
       </c>
       <c r="R14" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2704,32 +2704,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128747529</v>
+        <v>128747540</v>
       </c>
       <c r="B23" t="n">
-        <v>97576</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>740710</v>
+        <v>740713</v>
       </c>
       <c r="R23" t="n">
-        <v>7126339</v>
+        <v>7126372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2801,32 +2801,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128747540</v>
+        <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>97577</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740713</v>
+        <v>740710</v>
       </c>
       <c r="R24" t="n">
-        <v>7126372</v>
+        <v>7126339</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747526</v>
+        <v>128747542</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740633</v>
+        <v>740608</v>
       </c>
       <c r="R2" t="n">
-        <v>7126416</v>
+        <v>7126431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747542</v>
+        <v>128747526</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740608</v>
+        <v>740633</v>
       </c>
       <c r="R3" t="n">
-        <v>7126431</v>
+        <v>7126416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747515</v>
+        <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>92261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740774</v>
+        <v>740875</v>
       </c>
       <c r="R4" t="n">
-        <v>7126503</v>
+        <v>7126525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747520</v>
+        <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>92258</v>
+        <v>91507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740875</v>
+        <v>740774</v>
       </c>
       <c r="R5" t="n">
-        <v>7126525</v>
+        <v>7126503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>128747518</v>
       </c>
       <c r="B11" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128747530</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128747543</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128747539</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128747531</v>
+        <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>80146</v>
+        <v>91563</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2331,23 +2331,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2355,10 +2351,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>740934</v>
+        <v>740975</v>
       </c>
       <c r="R19" t="n">
-        <v>7126515</v>
+        <v>7126500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2417,10 +2413,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128747536</v>
+        <v>128747531</v>
       </c>
       <c r="B20" t="n">
-        <v>91560</v>
+        <v>80148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,19 +2424,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>740975</v>
+        <v>740934</v>
       </c>
       <c r="R20" t="n">
-        <v>7126500</v>
+        <v>7126515</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2513,7 +2513,7 @@
         <v>128747538</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>128747540</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747520</v>
+        <v>128747522</v>
       </c>
       <c r="B4" t="n">
-        <v>92261</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740875</v>
+        <v>740920</v>
       </c>
       <c r="R4" t="n">
-        <v>7126525</v>
+        <v>7126519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747515</v>
+        <v>128747527</v>
       </c>
       <c r="B5" t="n">
-        <v>91507</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740774</v>
+        <v>740608</v>
       </c>
       <c r="R5" t="n">
-        <v>7126503</v>
+        <v>7126469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747522</v>
+        <v>128747520</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>92261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740920</v>
+        <v>740875</v>
       </c>
       <c r="R6" t="n">
-        <v>7126519</v>
+        <v>7126525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747527</v>
+        <v>128747515</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>91507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740608</v>
+        <v>740774</v>
       </c>
       <c r="R7" t="n">
-        <v>7126469</v>
+        <v>7126503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2896,6 +2896,3376 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129472639</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>740720</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7126415</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129472644</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>740780</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7126388</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129472669</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>740693</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7126357</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre bohål av tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129472637</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>740653</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7126414</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129472659</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>740756</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7126511</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129472668</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>740760</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7126375</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129472636</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>740773</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7126518</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129472658</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>740964</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7126508</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129472628</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>741005</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7126520</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129472647</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97587</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>740823</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7126527</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129472626</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>740672</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7126349</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129472634</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>740970</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7126500</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129472656</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>740916</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7126531</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129472620</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91507</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>741005</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7126496</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129472665</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>740726</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7126418</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129472624</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92261</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>740880</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7126523</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129472630</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80177</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>740934</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7126499</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129472664</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>740964</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7126507</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129472641</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>740707</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7126416</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129472638</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>740703</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7126419</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129472629</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80177</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>740940</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7126498</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129472643</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>740770</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7126390</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129472651</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>740934</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7126501</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129472667</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>740732</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7126394</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129472631</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80177</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>740934</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7126501</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129472650</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>740934</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7126495</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129472623</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>740728</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7126370</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129472642</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>740685</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7126341</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129472635</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>740929</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7126517</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129472649</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>740947</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7126506</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129460734</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>740827</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7126414</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129457856</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>740471</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7126406</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129472622</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>741014</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7126495</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129472652</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80184</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>740945</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7126508</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128747542</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747522</v>
+        <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>92263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740920</v>
+        <v>740875</v>
       </c>
       <c r="R4" t="n">
-        <v>7126519</v>
+        <v>7126525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747527</v>
+        <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>91509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740608</v>
+        <v>740774</v>
       </c>
       <c r="R5" t="n">
-        <v>7126469</v>
+        <v>7126503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747520</v>
+        <v>128747527</v>
       </c>
       <c r="B6" t="n">
-        <v>92261</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740875</v>
+        <v>740608</v>
       </c>
       <c r="R6" t="n">
-        <v>7126525</v>
+        <v>7126469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747515</v>
+        <v>128747522</v>
       </c>
       <c r="B7" t="n">
-        <v>91507</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740774</v>
+        <v>740920</v>
       </c>
       <c r="R7" t="n">
-        <v>7126503</v>
+        <v>7126519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128747518</v>
+        <v>128747525</v>
       </c>
       <c r="B11" t="n">
-        <v>79662</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740764</v>
+        <v>740582</v>
       </c>
       <c r="R11" t="n">
-        <v>7126491</v>
+        <v>7126266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128747525</v>
+        <v>128747518</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740582</v>
+        <v>740764</v>
       </c>
       <c r="R12" t="n">
-        <v>7126266</v>
+        <v>7126491</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,7 +1741,7 @@
         <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128747530</v>
       </c>
       <c r="B14" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>128747543</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128747539</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>128747531</v>
       </c>
       <c r="B20" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>128747538</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>128747540</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472637</v>
+        <v>129472636</v>
       </c>
       <c r="B28" t="n">
         <v>57724</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740653</v>
+        <v>740773</v>
       </c>
       <c r="R28" t="n">
-        <v>7126414</v>
+        <v>7126518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472659</v>
+        <v>129472637</v>
       </c>
       <c r="B29" t="n">
-        <v>91563</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,33 +3319,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740756</v>
+        <v>740653</v>
       </c>
       <c r="R29" t="n">
-        <v>7126511</v>
+        <v>7126414</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3386,7 +3387,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472636</v>
+        <v>129472658</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>91565</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,23 +3526,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3550,10 +3546,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740773</v>
+        <v>740964</v>
       </c>
       <c r="R31" t="n">
-        <v>7126518</v>
+        <v>7126508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3612,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472658</v>
+        <v>129472659</v>
       </c>
       <c r="B32" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,16 +3633,19 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740964</v>
+        <v>740756</v>
       </c>
       <c r="R32" t="n">
-        <v>7126508</v>
+        <v>7126511</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,6 +3686,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472628</v>
+        <v>129472626</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741005</v>
+        <v>740672</v>
       </c>
       <c r="R33" t="n">
-        <v>7126520</v>
+        <v>7126349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472647</v>
+        <v>129472628</v>
       </c>
       <c r="B34" t="n">
-        <v>97587</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>740823</v>
+        <v>741005</v>
       </c>
       <c r="R34" t="n">
-        <v>7126527</v>
+        <v>7126520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472626</v>
+        <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>56917</v>
+        <v>97589</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>740672</v>
+        <v>740823</v>
       </c>
       <c r="R35" t="n">
-        <v>7126349</v>
+        <v>7126527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3996,32 +3996,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472634</v>
+        <v>129472620</v>
       </c>
       <c r="B36" t="n">
-        <v>57724</v>
+        <v>91509</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>740970</v>
+        <v>741005</v>
       </c>
       <c r="R36" t="n">
-        <v>7126500</v>
+        <v>7126496</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4093,53 +4093,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472656</v>
+        <v>129472665</v>
       </c>
       <c r="B37" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740916</v>
+        <v>740726</v>
       </c>
       <c r="R37" t="n">
-        <v>7126531</v>
+        <v>7126418</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4180,7 +4172,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4199,45 +4190,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472620</v>
+        <v>129472656</v>
       </c>
       <c r="B38" t="n">
-        <v>91507</v>
+        <v>98712</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741005</v>
+        <v>740916</v>
       </c>
       <c r="R38" t="n">
-        <v>7126496</v>
+        <v>7126531</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4278,6 +4277,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472665</v>
+        <v>129472634</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740726</v>
+        <v>740970</v>
       </c>
       <c r="R39" t="n">
-        <v>7126418</v>
+        <v>7126500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
         <v>129472624</v>
       </c>
       <c r="B40" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472630</v>
+        <v>129472641</v>
       </c>
       <c r="B41" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740934</v>
+        <v>740707</v>
       </c>
       <c r="R41" t="n">
-        <v>7126499</v>
+        <v>7126416</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4561,6 +4561,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4587,32 +4592,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472664</v>
+        <v>129472630</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>80178</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4627,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740964</v>
+        <v>740934</v>
       </c>
       <c r="R42" t="n">
-        <v>7126507</v>
+        <v>7126499</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4684,10 +4689,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472641</v>
+        <v>129472664</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4695,21 +4700,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4724,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740707</v>
+        <v>740964</v>
       </c>
       <c r="R43" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4755,11 +4760,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472638</v>
+        <v>129472643</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,16 +4797,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740703</v>
+        <v>740770</v>
       </c>
       <c r="R44" t="n">
-        <v>7126419</v>
+        <v>7126390</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4857,6 +4857,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4883,32 +4888,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472629</v>
+        <v>129472651</v>
       </c>
       <c r="B45" t="n">
-        <v>80177</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4923,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740940</v>
+        <v>740934</v>
       </c>
       <c r="R45" t="n">
-        <v>7126498</v>
+        <v>7126501</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,32 +4985,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129472643</v>
+        <v>129472629</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5015,10 +5020,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>740770</v>
+        <v>740940</v>
       </c>
       <c r="R46" t="n">
-        <v>7126390</v>
+        <v>7126498</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5051,11 +5056,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5082,32 +5082,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472651</v>
+        <v>129472631</v>
       </c>
       <c r="B47" t="n">
-        <v>80148</v>
+        <v>80178</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5182,7 +5182,7 @@
         <v>129472667</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472631</v>
+        <v>129472638</v>
       </c>
       <c r="B49" t="n">
-        <v>80177</v>
+        <v>57724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>740934</v>
+        <v>740703</v>
       </c>
       <c r="R49" t="n">
-        <v>7126501</v>
+        <v>7126419</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472650</v>
+        <v>129472623</v>
       </c>
       <c r="B50" t="n">
-        <v>80148</v>
+        <v>91545</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>740934</v>
+        <v>740728</v>
       </c>
       <c r="R50" t="n">
-        <v>7126495</v>
+        <v>7126370</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472623</v>
+        <v>129472650</v>
       </c>
       <c r="B51" t="n">
-        <v>91543</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>740728</v>
+        <v>740934</v>
       </c>
       <c r="R51" t="n">
-        <v>7126370</v>
+        <v>7126495</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
         <v>129472649</v>
       </c>
       <c r="B54" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5867,54 +5867,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129460734</v>
+        <v>129457856</v>
       </c>
       <c r="B55" t="n">
-        <v>98710</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>740827</v>
+        <v>740471</v>
       </c>
       <c r="R55" t="n">
-        <v>7126414</v>
+        <v>7126406</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5973,49 +5968,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129457856</v>
+        <v>129460734</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>98712</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>740471</v>
+        <v>740827</v>
       </c>
       <c r="R56" t="n">
-        <v>7126406</v>
+        <v>7126414</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6077,7 +6077,7 @@
         <v>129472622</v>
       </c>
       <c r="B57" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>129472652</v>
       </c>
       <c r="B58" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6265,6 +6265,103 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129472640</v>
+      </c>
+      <c r="B59" t="n">
+        <v>83010</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Invedatjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>740916</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7126502</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128747520</v>
       </c>
       <c r="B4" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747515</v>
       </c>
       <c r="B5" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747527</v>
+        <v>128747522</v>
       </c>
       <c r="B6" t="n">
         <v>57724</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740608</v>
+        <v>740920</v>
       </c>
       <c r="R6" t="n">
-        <v>7126469</v>
+        <v>7126519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747522</v>
+        <v>128747527</v>
       </c>
       <c r="B7" t="n">
         <v>57724</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740920</v>
+        <v>740608</v>
       </c>
       <c r="R7" t="n">
-        <v>7126519</v>
+        <v>7126469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128747525</v>
+        <v>128747518</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740582</v>
+        <v>740764</v>
       </c>
       <c r="R11" t="n">
-        <v>7126266</v>
+        <v>7126491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128747518</v>
+        <v>128747525</v>
       </c>
       <c r="B12" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740764</v>
+        <v>740582</v>
       </c>
       <c r="R12" t="n">
-        <v>7126491</v>
+        <v>7126266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,7 +1741,7 @@
         <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128747536</v>
       </c>
       <c r="B19" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>128747529</v>
       </c>
       <c r="B24" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472636</v>
+        <v>129472668</v>
       </c>
       <c r="B28" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,16 +3222,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3240,16 +3240,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740773</v>
+        <v>740760</v>
       </c>
       <c r="R28" t="n">
-        <v>7126518</v>
+        <v>7126375</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3282,6 +3290,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3308,10 +3321,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472637</v>
+        <v>129472659</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>91569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,34 +3332,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740653</v>
+        <v>740756</v>
       </c>
       <c r="R29" t="n">
-        <v>7126414</v>
+        <v>7126511</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3387,6 +3399,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3405,10 +3418,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472668</v>
+        <v>129472658</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91569</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,42 +3429,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740760</v>
+        <v>740964</v>
       </c>
       <c r="R30" t="n">
-        <v>7126375</v>
+        <v>7126508</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3484,11 +3485,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3515,10 +3511,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472658</v>
+        <v>129472636</v>
       </c>
       <c r="B31" t="n">
-        <v>91565</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,19 +3522,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740964</v>
+        <v>740773</v>
       </c>
       <c r="R31" t="n">
-        <v>7126508</v>
+        <v>7126518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472659</v>
+        <v>129472637</v>
       </c>
       <c r="B32" t="n">
-        <v>91565</v>
+        <v>57724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3619,33 +3619,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740756</v>
+        <v>740653</v>
       </c>
       <c r="R32" t="n">
-        <v>7126511</v>
+        <v>7126414</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3686,7 +3687,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472626</v>
+        <v>129472628</v>
       </c>
       <c r="B33" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>740672</v>
+        <v>741005</v>
       </c>
       <c r="R33" t="n">
-        <v>7126349</v>
+        <v>7126520</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472628</v>
+        <v>129472626</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741005</v>
+        <v>740672</v>
       </c>
       <c r="R34" t="n">
-        <v>7126520</v>
+        <v>7126349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
         <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,32 +3996,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472620</v>
+        <v>129472634</v>
       </c>
       <c r="B36" t="n">
-        <v>91509</v>
+        <v>57724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741005</v>
+        <v>740970</v>
       </c>
       <c r="R36" t="n">
-        <v>7126496</v>
+        <v>7126500</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,53 +4190,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472656</v>
+        <v>129472620</v>
       </c>
       <c r="B38" t="n">
-        <v>98712</v>
+        <v>91513</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>740916</v>
+        <v>741005</v>
       </c>
       <c r="R38" t="n">
-        <v>7126531</v>
+        <v>7126496</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4277,7 +4269,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4296,45 +4287,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472634</v>
+        <v>129472656</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>98716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740970</v>
+        <v>740916</v>
       </c>
       <c r="R39" t="n">
-        <v>7126500</v>
+        <v>7126531</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4375,6 +4374,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>129472624</v>
       </c>
       <c r="B40" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472641</v>
+        <v>129472664</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740707</v>
+        <v>740964</v>
       </c>
       <c r="R41" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4561,11 +4561,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4592,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472630</v>
+        <v>129472641</v>
       </c>
       <c r="B42" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4627,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740934</v>
+        <v>740707</v>
       </c>
       <c r="R42" t="n">
-        <v>7126499</v>
+        <v>7126416</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4663,6 +4658,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4689,32 +4689,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472664</v>
+        <v>129472630</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740964</v>
+        <v>740934</v>
       </c>
       <c r="R43" t="n">
-        <v>7126507</v>
+        <v>7126499</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472643</v>
+        <v>129472667</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740770</v>
+        <v>740732</v>
       </c>
       <c r="R44" t="n">
-        <v>7126390</v>
+        <v>7126394</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4857,11 +4857,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5179,10 +5174,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472667</v>
+        <v>129472638</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5190,21 +5185,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5214,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740732</v>
+        <v>740703</v>
       </c>
       <c r="R48" t="n">
-        <v>7126394</v>
+        <v>7126419</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5276,10 +5271,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472638</v>
+        <v>129472643</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5287,16 +5282,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5311,10 +5306,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>740703</v>
+        <v>740770</v>
       </c>
       <c r="R49" t="n">
-        <v>7126419</v>
+        <v>7126390</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5347,6 +5342,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472623</v>
+        <v>129472650</v>
       </c>
       <c r="B50" t="n">
-        <v>91545</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>740728</v>
+        <v>740934</v>
       </c>
       <c r="R50" t="n">
-        <v>7126370</v>
+        <v>7126495</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472650</v>
+        <v>129472623</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>91549</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>740934</v>
+        <v>740728</v>
       </c>
       <c r="R51" t="n">
-        <v>7126495</v>
+        <v>7126370</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5567,10 +5567,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129472642</v>
+        <v>129472635</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5578,16 +5578,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5596,20 +5596,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>740685</v>
+        <v>740929</v>
       </c>
       <c r="R52" t="n">
-        <v>7126341</v>
+        <v>7126517</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5642,11 +5638,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5673,10 +5664,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129472635</v>
+        <v>129472642</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5684,16 +5675,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5702,16 +5693,20 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>740929</v>
+        <v>740685</v>
       </c>
       <c r="R53" t="n">
-        <v>7126517</v>
+        <v>7126341</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5744,6 +5739,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5971,7 +5971,7 @@
         <v>129460734</v>
       </c>
       <c r="B56" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>129472622</v>
       </c>
       <c r="B57" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128747520</v>
+        <v>128747522</v>
       </c>
       <c r="B4" t="n">
-        <v>92267</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740875</v>
+        <v>740920</v>
       </c>
       <c r="R4" t="n">
-        <v>7126525</v>
+        <v>7126519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128747515</v>
+        <v>128747527</v>
       </c>
       <c r="B5" t="n">
-        <v>91513</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740774</v>
+        <v>740608</v>
       </c>
       <c r="R5" t="n">
-        <v>7126503</v>
+        <v>7126469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128747522</v>
+        <v>128747515</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>91514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740920</v>
+        <v>740774</v>
       </c>
       <c r="R6" t="n">
-        <v>7126519</v>
+        <v>7126503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747527</v>
+        <v>128747520</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>92268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740608</v>
+        <v>740875</v>
       </c>
       <c r="R7" t="n">
-        <v>7126469</v>
+        <v>7126525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128747519</v>
       </c>
       <c r="B8" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128747537</v>
       </c>
       <c r="B9" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>128747517</v>
       </c>
       <c r="B13" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>128747516</v>
       </c>
       <c r="B17" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128747536</v>
+        <v>128747531</v>
       </c>
       <c r="B19" t="n">
-        <v>91569</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2331,19 +2331,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2351,10 +2355,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>740975</v>
+        <v>740934</v>
       </c>
       <c r="R19" t="n">
-        <v>7126500</v>
+        <v>7126515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2413,10 +2417,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128747531</v>
+        <v>128747536</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>91570</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2424,23 +2428,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>740934</v>
+        <v>740975</v>
       </c>
       <c r="R20" t="n">
-        <v>7126515</v>
+        <v>7126500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2704,32 +2704,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128747540</v>
+        <v>128747529</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>740713</v>
+        <v>740710</v>
       </c>
       <c r="R23" t="n">
-        <v>7126372</v>
+        <v>7126339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2801,32 +2801,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128747529</v>
+        <v>128747540</v>
       </c>
       <c r="B24" t="n">
-        <v>97587</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740710</v>
+        <v>740713</v>
       </c>
       <c r="R24" t="n">
-        <v>7126339</v>
+        <v>7126372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472659</v>
+        <v>129472636</v>
       </c>
       <c r="B29" t="n">
-        <v>91569</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3332,33 +3332,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740756</v>
+        <v>740773</v>
       </c>
       <c r="R29" t="n">
-        <v>7126511</v>
+        <v>7126518</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3399,7 +3400,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472658</v>
+        <v>129472637</v>
       </c>
       <c r="B30" t="n">
-        <v>91569</v>
+        <v>57724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3429,19 +3429,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3449,10 +3453,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740964</v>
+        <v>740653</v>
       </c>
       <c r="R30" t="n">
-        <v>7126508</v>
+        <v>7126414</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3511,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472636</v>
+        <v>129472658</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>91570</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3522,23 +3526,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740773</v>
+        <v>740964</v>
       </c>
       <c r="R31" t="n">
-        <v>7126518</v>
+        <v>7126508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472637</v>
+        <v>129472659</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>91570</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3619,34 +3619,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740653</v>
+        <v>740756</v>
       </c>
       <c r="R32" t="n">
-        <v>7126414</v>
+        <v>7126511</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,6 +3686,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472628</v>
+        <v>129472626</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741005</v>
+        <v>740672</v>
       </c>
       <c r="R33" t="n">
-        <v>7126520</v>
+        <v>7126349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472626</v>
+        <v>129472647</v>
       </c>
       <c r="B34" t="n">
-        <v>56917</v>
+        <v>97601</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>740672</v>
+        <v>740823</v>
       </c>
       <c r="R34" t="n">
-        <v>7126349</v>
+        <v>7126527</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3899,32 +3899,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472647</v>
+        <v>129472628</v>
       </c>
       <c r="B35" t="n">
-        <v>97593</v>
+        <v>57887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>740823</v>
+        <v>741005</v>
       </c>
       <c r="R35" t="n">
-        <v>7126527</v>
+        <v>7126520</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472634</v>
+        <v>129472665</v>
       </c>
       <c r="B36" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4007,21 +4007,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>740970</v>
+        <v>740726</v>
       </c>
       <c r="R36" t="n">
-        <v>7126500</v>
+        <v>7126418</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4093,45 +4093,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472665</v>
+        <v>129472656</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740726</v>
+        <v>740916</v>
       </c>
       <c r="R37" t="n">
-        <v>7126418</v>
+        <v>7126531</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4172,6 +4180,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4190,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472620</v>
+        <v>129472634</v>
       </c>
       <c r="B38" t="n">
-        <v>91513</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4225,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741005</v>
+        <v>740970</v>
       </c>
       <c r="R38" t="n">
-        <v>7126496</v>
+        <v>7126500</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4287,53 +4296,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472656</v>
+        <v>129472620</v>
       </c>
       <c r="B39" t="n">
-        <v>98716</v>
+        <v>91514</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740916</v>
+        <v>741005</v>
       </c>
       <c r="R39" t="n">
-        <v>7126531</v>
+        <v>7126496</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4374,7 +4375,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>129472624</v>
       </c>
       <c r="B40" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472667</v>
+        <v>129472638</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740732</v>
+        <v>740703</v>
       </c>
       <c r="R44" t="n">
-        <v>7126394</v>
+        <v>7126419</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472651</v>
+        <v>129472667</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740934</v>
+        <v>740732</v>
       </c>
       <c r="R45" t="n">
-        <v>7126501</v>
+        <v>7126394</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5077,32 +5077,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472631</v>
+        <v>129472651</v>
       </c>
       <c r="B47" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5174,32 +5174,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472638</v>
+        <v>129472631</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>80178</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740703</v>
+        <v>740934</v>
       </c>
       <c r="R48" t="n">
-        <v>7126419</v>
+        <v>7126501</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472650</v>
+        <v>129472623</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>740934</v>
+        <v>740728</v>
       </c>
       <c r="R50" t="n">
-        <v>7126495</v>
+        <v>7126370</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472623</v>
+        <v>129472650</v>
       </c>
       <c r="B51" t="n">
-        <v>91549</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>740728</v>
+        <v>740934</v>
       </c>
       <c r="R51" t="n">
-        <v>7126370</v>
+        <v>7126495</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5567,10 +5567,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129472635</v>
+        <v>129472642</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5578,16 +5578,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5596,16 +5596,20 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>740929</v>
+        <v>740685</v>
       </c>
       <c r="R52" t="n">
-        <v>7126517</v>
+        <v>7126341</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5638,6 +5642,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5664,10 +5673,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129472642</v>
+        <v>129472635</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5675,16 +5684,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5693,20 +5702,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>740685</v>
+        <v>740929</v>
       </c>
       <c r="R53" t="n">
-        <v>7126341</v>
+        <v>7126517</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5739,11 +5744,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5971,7 +5971,7 @@
         <v>129460734</v>
       </c>
       <c r="B56" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>129472622</v>
       </c>
       <c r="B57" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472668</v>
+        <v>129472636</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,16 +3222,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3240,24 +3240,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740760</v>
+        <v>740773</v>
       </c>
       <c r="R28" t="n">
-        <v>7126375</v>
+        <v>7126518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3290,11 +3282,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3321,7 +3308,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472636</v>
+        <v>129472637</v>
       </c>
       <c r="B29" t="n">
         <v>57724</v>
@@ -3356,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740773</v>
+        <v>740653</v>
       </c>
       <c r="R29" t="n">
-        <v>7126518</v>
+        <v>7126414</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3418,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472637</v>
+        <v>129472668</v>
       </c>
       <c r="B30" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3429,16 +3416,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3447,16 +3434,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740653</v>
+        <v>740760</v>
       </c>
       <c r="R30" t="n">
-        <v>7126414</v>
+        <v>7126375</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3489,6 +3484,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3515,7 +3515,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472658</v>
+        <v>129472659</v>
       </c>
       <c r="B31" t="n">
         <v>91570</v>
@@ -3540,16 +3540,19 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740964</v>
+        <v>740756</v>
       </c>
       <c r="R31" t="n">
-        <v>7126508</v>
+        <v>7126511</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,6 +3593,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3608,7 +3612,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472659</v>
+        <v>129472658</v>
       </c>
       <c r="B32" t="n">
         <v>91570</v>
@@ -3633,19 +3637,16 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740756</v>
+        <v>740964</v>
       </c>
       <c r="R32" t="n">
-        <v>7126511</v>
+        <v>7126508</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3686,7 +3687,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472634</v>
+        <v>129472620</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>91514</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>740970</v>
+        <v>741005</v>
       </c>
       <c r="R38" t="n">
-        <v>7126500</v>
+        <v>7126496</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4296,32 +4296,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472620</v>
+        <v>129472634</v>
       </c>
       <c r="B39" t="n">
-        <v>91514</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741005</v>
+        <v>740970</v>
       </c>
       <c r="R39" t="n">
-        <v>7126496</v>
+        <v>7126500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472641</v>
+        <v>129472630</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740707</v>
+        <v>740934</v>
       </c>
       <c r="R42" t="n">
-        <v>7126416</v>
+        <v>7126499</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4658,11 +4658,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4689,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472630</v>
+        <v>129472641</v>
       </c>
       <c r="B43" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4724,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740934</v>
+        <v>740707</v>
       </c>
       <c r="R43" t="n">
-        <v>7126499</v>
+        <v>7126416</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4760,6 +4755,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472638</v>
+        <v>129472667</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740703</v>
+        <v>740732</v>
       </c>
       <c r="R44" t="n">
-        <v>7126419</v>
+        <v>7126394</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472667</v>
+        <v>129472651</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740732</v>
+        <v>740934</v>
       </c>
       <c r="R45" t="n">
-        <v>7126394</v>
+        <v>7126501</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5077,32 +5077,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472651</v>
+        <v>129472631</v>
       </c>
       <c r="B47" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5174,32 +5174,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472631</v>
+        <v>129472638</v>
       </c>
       <c r="B48" t="n">
-        <v>80178</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740934</v>
+        <v>740703</v>
       </c>
       <c r="R48" t="n">
-        <v>7126501</v>
+        <v>7126419</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5567,10 +5567,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129472642</v>
+        <v>129472635</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5578,16 +5578,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5596,20 +5596,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>740685</v>
+        <v>740929</v>
       </c>
       <c r="R52" t="n">
-        <v>7126341</v>
+        <v>7126517</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5642,11 +5638,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5673,10 +5664,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129472635</v>
+        <v>129472642</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5684,16 +5675,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5702,16 +5693,20 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>740929</v>
+        <v>740685</v>
       </c>
       <c r="R53" t="n">
-        <v>7126517</v>
+        <v>7126341</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5744,6 +5739,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472626</v>
+        <v>129472628</v>
       </c>
       <c r="B33" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>740672</v>
+        <v>741005</v>
       </c>
       <c r="R33" t="n">
-        <v>7126349</v>
+        <v>7126520</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472647</v>
+        <v>129472626</v>
       </c>
       <c r="B34" t="n">
-        <v>97601</v>
+        <v>56917</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>740823</v>
+        <v>740672</v>
       </c>
       <c r="R34" t="n">
-        <v>7126527</v>
+        <v>7126349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3899,32 +3899,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472628</v>
+        <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>57887</v>
+        <v>97601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741005</v>
+        <v>740823</v>
       </c>
       <c r="R35" t="n">
-        <v>7126520</v>
+        <v>7126527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3996,45 +3996,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472665</v>
+        <v>129472656</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>740726</v>
+        <v>740916</v>
       </c>
       <c r="R36" t="n">
-        <v>7126418</v>
+        <v>7126531</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,6 +4083,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4093,53 +4102,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472656</v>
+        <v>129472665</v>
       </c>
       <c r="B37" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740916</v>
+        <v>740726</v>
       </c>
       <c r="R37" t="n">
-        <v>7126531</v>
+        <v>7126418</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4180,7 +4181,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472664</v>
+        <v>129472641</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740964</v>
+        <v>740707</v>
       </c>
       <c r="R41" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4561,6 +4561,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4587,32 +4592,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472630</v>
+        <v>129472664</v>
       </c>
       <c r="B42" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4627,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740934</v>
+        <v>740964</v>
       </c>
       <c r="R42" t="n">
-        <v>7126499</v>
+        <v>7126507</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4684,32 +4689,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472641</v>
+        <v>129472630</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4724,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740707</v>
+        <v>740934</v>
       </c>
       <c r="R43" t="n">
-        <v>7126416</v>
+        <v>7126499</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4755,11 +4760,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5867,49 +5867,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129457856</v>
+        <v>129460734</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>98724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>740471</v>
+        <v>740827</v>
       </c>
       <c r="R55" t="n">
-        <v>7126406</v>
+        <v>7126414</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5968,54 +5973,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129460734</v>
+        <v>129457856</v>
       </c>
       <c r="B56" t="n">
-        <v>98724</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>740827</v>
+        <v>740471</v>
       </c>
       <c r="R56" t="n">
-        <v>7126414</v>
+        <v>7126406</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3515,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472659</v>
+        <v>129472658</v>
       </c>
       <c r="B31" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3540,19 +3540,16 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740756</v>
+        <v>740964</v>
       </c>
       <c r="R31" t="n">
-        <v>7126511</v>
+        <v>7126508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3593,7 +3590,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3612,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472658</v>
+        <v>129472659</v>
       </c>
       <c r="B32" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,16 +3633,19 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740964</v>
+        <v>740756</v>
       </c>
       <c r="R32" t="n">
-        <v>7126508</v>
+        <v>7126511</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,6 +3686,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472628</v>
+        <v>129472626</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741005</v>
+        <v>740672</v>
       </c>
       <c r="R33" t="n">
-        <v>7126520</v>
+        <v>7126349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472626</v>
+        <v>129472628</v>
       </c>
       <c r="B34" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>740672</v>
+        <v>741005</v>
       </c>
       <c r="R34" t="n">
-        <v>7126349</v>
+        <v>7126520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
         <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>129472656</v>
       </c>
       <c r="B36" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472620</v>
+        <v>129472634</v>
       </c>
       <c r="B38" t="n">
-        <v>91514</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741005</v>
+        <v>740970</v>
       </c>
       <c r="R38" t="n">
-        <v>7126496</v>
+        <v>7126500</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4296,32 +4296,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472634</v>
+        <v>129472620</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>91517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740970</v>
+        <v>741005</v>
       </c>
       <c r="R39" t="n">
-        <v>7126500</v>
+        <v>7126496</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
         <v>129472624</v>
       </c>
       <c r="B40" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472641</v>
+        <v>129472630</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740707</v>
+        <v>740934</v>
       </c>
       <c r="R41" t="n">
-        <v>7126416</v>
+        <v>7126499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4561,11 +4561,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4689,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472630</v>
+        <v>129472641</v>
       </c>
       <c r="B43" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4724,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740934</v>
+        <v>740707</v>
       </c>
       <c r="R43" t="n">
-        <v>7126499</v>
+        <v>7126416</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4760,6 +4755,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472667</v>
+        <v>129472651</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740732</v>
+        <v>740934</v>
       </c>
       <c r="R44" t="n">
-        <v>7126394</v>
+        <v>7126501</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,32 +4883,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472651</v>
+        <v>129472629</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740934</v>
+        <v>740940</v>
       </c>
       <c r="R45" t="n">
-        <v>7126501</v>
+        <v>7126498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129472629</v>
+        <v>129472631</v>
       </c>
       <c r="B46" t="n">
         <v>80178</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>740940</v>
+        <v>740934</v>
       </c>
       <c r="R46" t="n">
-        <v>7126498</v>
+        <v>7126501</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5077,32 +5077,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472631</v>
+        <v>129472667</v>
       </c>
       <c r="B47" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740934</v>
+        <v>740732</v>
       </c>
       <c r="R47" t="n">
-        <v>7126501</v>
+        <v>7126394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472623</v>
+        <v>129472650</v>
       </c>
       <c r="B50" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>740728</v>
+        <v>740934</v>
       </c>
       <c r="R50" t="n">
-        <v>7126370</v>
+        <v>7126495</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472650</v>
+        <v>129472623</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>740934</v>
+        <v>740728</v>
       </c>
       <c r="R51" t="n">
-        <v>7126495</v>
+        <v>7126370</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5567,10 +5567,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129472635</v>
+        <v>129472642</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5578,16 +5578,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5596,16 +5596,20 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>740929</v>
+        <v>740685</v>
       </c>
       <c r="R52" t="n">
-        <v>7126517</v>
+        <v>7126341</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5638,6 +5642,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5664,10 +5673,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129472642</v>
+        <v>129472635</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5675,16 +5684,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5693,20 +5702,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>740685</v>
+        <v>740929</v>
       </c>
       <c r="R53" t="n">
-        <v>7126341</v>
+        <v>7126517</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5739,11 +5744,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5867,54 +5867,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129460734</v>
+        <v>129457856</v>
       </c>
       <c r="B55" t="n">
-        <v>98724</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>740827</v>
+        <v>740471</v>
       </c>
       <c r="R55" t="n">
-        <v>7126414</v>
+        <v>7126406</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5973,49 +5968,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129457856</v>
+        <v>129460734</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>740471</v>
+        <v>740827</v>
       </c>
       <c r="R56" t="n">
-        <v>7126406</v>
+        <v>7126414</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6077,7 +6077,7 @@
         <v>129472622</v>
       </c>
       <c r="B57" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472636</v>
+        <v>129472658</v>
       </c>
       <c r="B28" t="n">
-        <v>57724</v>
+        <v>91573</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,23 +3222,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3246,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740773</v>
+        <v>740964</v>
       </c>
       <c r="R28" t="n">
-        <v>7126518</v>
+        <v>7126508</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3304,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472637</v>
+        <v>129472659</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>91573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,34 +3315,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740653</v>
+        <v>740756</v>
       </c>
       <c r="R29" t="n">
-        <v>7126414</v>
+        <v>7126511</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3387,6 +3382,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3405,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472668</v>
+        <v>129472636</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,16 +3412,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3434,24 +3430,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740760</v>
+        <v>740773</v>
       </c>
       <c r="R30" t="n">
-        <v>7126375</v>
+        <v>7126518</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3484,11 +3472,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3515,10 +3498,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472658</v>
+        <v>129472637</v>
       </c>
       <c r="B31" t="n">
-        <v>91573</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,19 +3509,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3546,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740964</v>
+        <v>740653</v>
       </c>
       <c r="R31" t="n">
-        <v>7126508</v>
+        <v>7126414</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3608,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472659</v>
+        <v>129472668</v>
       </c>
       <c r="B32" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3619,22 +3606,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3642,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740756</v>
+        <v>740760</v>
       </c>
       <c r="R32" t="n">
-        <v>7126511</v>
+        <v>7126375</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3680,13 +3676,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3996,53 +3996,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472656</v>
+        <v>129472620</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>740916</v>
+        <v>741005</v>
       </c>
       <c r="R36" t="n">
-        <v>7126531</v>
+        <v>7126496</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4083,7 +4075,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4296,45 +4287,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472620</v>
+        <v>129472656</v>
       </c>
       <c r="B39" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741005</v>
+        <v>740916</v>
       </c>
       <c r="R39" t="n">
-        <v>7126496</v>
+        <v>7126531</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4375,6 +4374,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472630</v>
+        <v>129472664</v>
       </c>
       <c r="B41" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740934</v>
+        <v>740964</v>
       </c>
       <c r="R41" t="n">
-        <v>7126499</v>
+        <v>7126507</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472664</v>
+        <v>129472630</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740964</v>
+        <v>740934</v>
       </c>
       <c r="R42" t="n">
-        <v>7126507</v>
+        <v>7126499</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472651</v>
+        <v>129472667</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740934</v>
+        <v>740732</v>
       </c>
       <c r="R44" t="n">
-        <v>7126501</v>
+        <v>7126394</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,32 +4883,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472629</v>
+        <v>129472638</v>
       </c>
       <c r="B45" t="n">
-        <v>80178</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740940</v>
+        <v>740703</v>
       </c>
       <c r="R45" t="n">
-        <v>7126498</v>
+        <v>7126419</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,32 +4980,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129472631</v>
+        <v>129472643</v>
       </c>
       <c r="B46" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>740934</v>
+        <v>740770</v>
       </c>
       <c r="R46" t="n">
-        <v>7126501</v>
+        <v>7126390</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5051,6 +5051,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5077,10 +5082,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472667</v>
+        <v>129472651</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5088,21 +5093,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5112,10 +5117,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740732</v>
+        <v>740934</v>
       </c>
       <c r="R47" t="n">
-        <v>7126394</v>
+        <v>7126501</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5174,32 +5179,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472638</v>
+        <v>129472629</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>80178</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5214,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740703</v>
+        <v>740940</v>
       </c>
       <c r="R48" t="n">
-        <v>7126419</v>
+        <v>7126498</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5271,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472643</v>
+        <v>129472631</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5306,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>740770</v>
+        <v>740934</v>
       </c>
       <c r="R49" t="n">
-        <v>7126390</v>
+        <v>7126501</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5342,11 +5347,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472650</v>
+        <v>129472623</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>740934</v>
+        <v>740728</v>
       </c>
       <c r="R50" t="n">
-        <v>7126495</v>
+        <v>7126370</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472623</v>
+        <v>129472650</v>
       </c>
       <c r="B51" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>740728</v>
+        <v>740934</v>
       </c>
       <c r="R51" t="n">
-        <v>7126370</v>
+        <v>7126495</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5867,49 +5867,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129457856</v>
+        <v>129460734</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>740471</v>
+        <v>740827</v>
       </c>
       <c r="R55" t="n">
-        <v>7126406</v>
+        <v>7126414</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5968,54 +5973,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129460734</v>
+        <v>129457856</v>
       </c>
       <c r="B56" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>740827</v>
+        <v>740471</v>
       </c>
       <c r="R56" t="n">
-        <v>7126414</v>
+        <v>7126406</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472626</v>
+        <v>129472628</v>
       </c>
       <c r="B33" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>740672</v>
+        <v>741005</v>
       </c>
       <c r="R33" t="n">
-        <v>7126349</v>
+        <v>7126520</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472628</v>
+        <v>129472647</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>97604</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741005</v>
+        <v>740823</v>
       </c>
       <c r="R34" t="n">
-        <v>7126520</v>
+        <v>7126527</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472647</v>
+        <v>129472626</v>
       </c>
       <c r="B35" t="n">
-        <v>97604</v>
+        <v>56917</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>740823</v>
+        <v>740672</v>
       </c>
       <c r="R35" t="n">
-        <v>7126527</v>
+        <v>7126349</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3996,32 +3996,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472620</v>
+        <v>129472634</v>
       </c>
       <c r="B36" t="n">
-        <v>91517</v>
+        <v>57724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741005</v>
+        <v>740970</v>
       </c>
       <c r="R36" t="n">
-        <v>7126496</v>
+        <v>7126500</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4093,45 +4093,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472665</v>
+        <v>129472656</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740726</v>
+        <v>740916</v>
       </c>
       <c r="R37" t="n">
-        <v>7126418</v>
+        <v>7126531</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4172,6 +4180,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4190,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472634</v>
+        <v>129472620</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>91517</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4225,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>740970</v>
+        <v>741005</v>
       </c>
       <c r="R38" t="n">
-        <v>7126500</v>
+        <v>7126496</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4287,53 +4296,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472656</v>
+        <v>129472665</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740916</v>
+        <v>740726</v>
       </c>
       <c r="R39" t="n">
-        <v>7126531</v>
+        <v>7126418</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4374,7 +4375,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472664</v>
+        <v>129472630</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740964</v>
+        <v>740934</v>
       </c>
       <c r="R41" t="n">
-        <v>7126507</v>
+        <v>7126499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472630</v>
+        <v>129472664</v>
       </c>
       <c r="B42" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740934</v>
+        <v>740964</v>
       </c>
       <c r="R42" t="n">
-        <v>7126499</v>
+        <v>7126507</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4786,32 +4786,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472667</v>
+        <v>129472629</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740732</v>
+        <v>740940</v>
       </c>
       <c r="R44" t="n">
-        <v>7126394</v>
+        <v>7126498</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472638</v>
+        <v>129472651</v>
       </c>
       <c r="B45" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740703</v>
+        <v>740934</v>
       </c>
       <c r="R45" t="n">
-        <v>7126419</v>
+        <v>7126501</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,32 +4980,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129472643</v>
+        <v>129472631</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>740770</v>
+        <v>740934</v>
       </c>
       <c r="R46" t="n">
-        <v>7126390</v>
+        <v>7126501</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5051,11 +5051,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5082,10 +5077,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472651</v>
+        <v>129472667</v>
       </c>
       <c r="B47" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5093,21 +5088,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5117,10 +5112,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740934</v>
+        <v>740732</v>
       </c>
       <c r="R47" t="n">
-        <v>7126501</v>
+        <v>7126394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5179,32 +5174,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472629</v>
+        <v>129472638</v>
       </c>
       <c r="B48" t="n">
-        <v>80178</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5214,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740940</v>
+        <v>740703</v>
       </c>
       <c r="R48" t="n">
-        <v>7126498</v>
+        <v>7126419</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5276,32 +5271,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472631</v>
+        <v>129472643</v>
       </c>
       <c r="B49" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5306,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>740934</v>
+        <v>740770</v>
       </c>
       <c r="R49" t="n">
-        <v>7126501</v>
+        <v>7126390</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5347,6 +5342,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472623</v>
+        <v>129472650</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>740728</v>
+        <v>740934</v>
       </c>
       <c r="R50" t="n">
-        <v>7126370</v>
+        <v>7126495</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472650</v>
+        <v>129472623</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>740934</v>
+        <v>740728</v>
       </c>
       <c r="R51" t="n">
-        <v>7126495</v>
+        <v>7126370</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5567,10 +5567,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129472642</v>
+        <v>129472635</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5578,16 +5578,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5596,20 +5596,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>740685</v>
+        <v>740929</v>
       </c>
       <c r="R52" t="n">
-        <v>7126341</v>
+        <v>7126517</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5642,11 +5638,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5673,10 +5664,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129472635</v>
+        <v>129472642</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5684,16 +5675,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5702,16 +5693,20 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>740929</v>
+        <v>740685</v>
       </c>
       <c r="R53" t="n">
-        <v>7126517</v>
+        <v>7126341</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5744,6 +5739,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5867,54 +5867,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129460734</v>
+        <v>129457856</v>
       </c>
       <c r="B55" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>740827</v>
+        <v>740471</v>
       </c>
       <c r="R55" t="n">
-        <v>7126414</v>
+        <v>7126406</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5973,49 +5968,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129457856</v>
+        <v>129460734</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>740471</v>
+        <v>740827</v>
       </c>
       <c r="R56" t="n">
-        <v>7126406</v>
+        <v>7126414</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472628</v>
+        <v>129472626</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741005</v>
+        <v>740672</v>
       </c>
       <c r="R33" t="n">
-        <v>7126520</v>
+        <v>7126349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472647</v>
+        <v>129472628</v>
       </c>
       <c r="B34" t="n">
-        <v>97604</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>740823</v>
+        <v>741005</v>
       </c>
       <c r="R34" t="n">
-        <v>7126527</v>
+        <v>7126520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472626</v>
+        <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>56917</v>
+        <v>97604</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>740672</v>
+        <v>740823</v>
       </c>
       <c r="R35" t="n">
-        <v>7126349</v>
+        <v>7126527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472634</v>
+        <v>129472665</v>
       </c>
       <c r="B36" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4007,21 +4007,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>740970</v>
+        <v>740726</v>
       </c>
       <c r="R36" t="n">
-        <v>7126500</v>
+        <v>7126418</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4093,53 +4093,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472656</v>
+        <v>129472620</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740916</v>
+        <v>741005</v>
       </c>
       <c r="R37" t="n">
-        <v>7126531</v>
+        <v>7126496</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4180,7 +4172,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4199,45 +4190,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472620</v>
+        <v>129472656</v>
       </c>
       <c r="B38" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741005</v>
+        <v>740916</v>
       </c>
       <c r="R38" t="n">
-        <v>7126496</v>
+        <v>7126531</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4278,6 +4277,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472665</v>
+        <v>129472634</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740726</v>
+        <v>740970</v>
       </c>
       <c r="R39" t="n">
-        <v>7126418</v>
+        <v>7126500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472630</v>
+        <v>129472641</v>
       </c>
       <c r="B41" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740934</v>
+        <v>740707</v>
       </c>
       <c r="R41" t="n">
-        <v>7126499</v>
+        <v>7126416</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4561,6 +4561,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4587,32 +4592,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472664</v>
+        <v>129472630</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4627,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740964</v>
+        <v>740934</v>
       </c>
       <c r="R42" t="n">
-        <v>7126507</v>
+        <v>7126499</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4684,10 +4689,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472641</v>
+        <v>129472664</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4695,21 +4700,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4724,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740707</v>
+        <v>740964</v>
       </c>
       <c r="R43" t="n">
-        <v>7126416</v>
+        <v>7126507</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4755,11 +4760,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4786,32 +4786,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472629</v>
+        <v>129472667</v>
       </c>
       <c r="B44" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740940</v>
+        <v>740732</v>
       </c>
       <c r="R44" t="n">
-        <v>7126498</v>
+        <v>7126394</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472651</v>
+        <v>129472638</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740934</v>
+        <v>740703</v>
       </c>
       <c r="R45" t="n">
-        <v>7126501</v>
+        <v>7126419</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,32 +4980,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129472631</v>
+        <v>129472651</v>
       </c>
       <c r="B46" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5077,32 +5077,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472667</v>
+        <v>129472629</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740732</v>
+        <v>740940</v>
       </c>
       <c r="R47" t="n">
-        <v>7126394</v>
+        <v>7126498</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5174,32 +5174,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472638</v>
+        <v>129472631</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>80178</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740703</v>
+        <v>740934</v>
       </c>
       <c r="R48" t="n">
-        <v>7126419</v>
+        <v>7126501</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472658</v>
+        <v>129472636</v>
       </c>
       <c r="B28" t="n">
-        <v>91573</v>
+        <v>57724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,19 +3222,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3242,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740964</v>
+        <v>740773</v>
       </c>
       <c r="R28" t="n">
-        <v>7126508</v>
+        <v>7126518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472659</v>
+        <v>129472637</v>
       </c>
       <c r="B29" t="n">
-        <v>91573</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3315,33 +3319,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740756</v>
+        <v>740653</v>
       </c>
       <c r="R29" t="n">
-        <v>7126511</v>
+        <v>7126414</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3382,7 +3387,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3401,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472636</v>
+        <v>129472668</v>
       </c>
       <c r="B30" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,16 +3416,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3430,16 +3434,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740773</v>
+        <v>740760</v>
       </c>
       <c r="R30" t="n">
-        <v>7126518</v>
+        <v>7126375</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3472,6 +3484,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3498,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472637</v>
+        <v>129472658</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>91573</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3509,23 +3526,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3533,10 +3546,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740653</v>
+        <v>740964</v>
       </c>
       <c r="R31" t="n">
-        <v>7126414</v>
+        <v>7126508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3595,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472668</v>
+        <v>129472659</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,31 +3619,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3638,10 +3642,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740760</v>
+        <v>740756</v>
       </c>
       <c r="R32" t="n">
-        <v>7126375</v>
+        <v>7126511</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3676,17 +3680,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472626</v>
+        <v>129472628</v>
       </c>
       <c r="B33" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>740672</v>
+        <v>741005</v>
       </c>
       <c r="R33" t="n">
-        <v>7126349</v>
+        <v>7126520</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472628</v>
+        <v>129472626</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741005</v>
+        <v>740672</v>
       </c>
       <c r="R34" t="n">
-        <v>7126520</v>
+        <v>7126349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3996,45 +3996,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472665</v>
+        <v>129472656</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>740726</v>
+        <v>740916</v>
       </c>
       <c r="R36" t="n">
-        <v>7126418</v>
+        <v>7126531</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,6 +4083,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4093,32 +4102,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472620</v>
+        <v>129472665</v>
       </c>
       <c r="B37" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4128,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>741005</v>
+        <v>740726</v>
       </c>
       <c r="R37" t="n">
-        <v>7126496</v>
+        <v>7126418</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4190,53 +4199,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472656</v>
+        <v>129472620</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>740916</v>
+        <v>741005</v>
       </c>
       <c r="R38" t="n">
-        <v>7126531</v>
+        <v>7126496</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4277,7 +4278,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4592,32 +4592,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472630</v>
+        <v>129472664</v>
       </c>
       <c r="B42" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740934</v>
+        <v>740964</v>
       </c>
       <c r="R42" t="n">
-        <v>7126499</v>
+        <v>7126507</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4689,32 +4689,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472664</v>
+        <v>129472630</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740964</v>
+        <v>740934</v>
       </c>
       <c r="R43" t="n">
-        <v>7126507</v>
+        <v>7126499</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472638</v>
+        <v>129472651</v>
       </c>
       <c r="B45" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740703</v>
+        <v>740934</v>
       </c>
       <c r="R45" t="n">
-        <v>7126419</v>
+        <v>7126501</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,32 +4980,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129472651</v>
+        <v>129472629</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>740934</v>
+        <v>740940</v>
       </c>
       <c r="R46" t="n">
-        <v>7126501</v>
+        <v>7126498</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472629</v>
+        <v>129472631</v>
       </c>
       <c r="B47" t="n">
         <v>80178</v>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740940</v>
+        <v>740934</v>
       </c>
       <c r="R47" t="n">
-        <v>7126498</v>
+        <v>7126501</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5174,32 +5174,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472631</v>
+        <v>129472638</v>
       </c>
       <c r="B48" t="n">
-        <v>80178</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740934</v>
+        <v>740703</v>
       </c>
       <c r="R48" t="n">
-        <v>7126501</v>
+        <v>7126419</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472650</v>
+        <v>129472623</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>740934</v>
+        <v>740728</v>
       </c>
       <c r="R50" t="n">
-        <v>7126495</v>
+        <v>7126370</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472623</v>
+        <v>129472650</v>
       </c>
       <c r="B51" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>740728</v>
+        <v>740934</v>
       </c>
       <c r="R51" t="n">
-        <v>7126370</v>
+        <v>7126495</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472636</v>
+        <v>129472658</v>
       </c>
       <c r="B28" t="n">
-        <v>57724</v>
+        <v>91573</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,23 +3222,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3246,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740773</v>
+        <v>740964</v>
       </c>
       <c r="R28" t="n">
-        <v>7126518</v>
+        <v>7126508</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3304,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472637</v>
+        <v>129472659</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>91573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,34 +3315,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740653</v>
+        <v>740756</v>
       </c>
       <c r="R29" t="n">
-        <v>7126414</v>
+        <v>7126511</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3387,6 +3382,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3515,10 +3511,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472658</v>
+        <v>129472636</v>
       </c>
       <c r="B31" t="n">
-        <v>91573</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,19 +3522,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740964</v>
+        <v>740773</v>
       </c>
       <c r="R31" t="n">
-        <v>7126508</v>
+        <v>7126518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472659</v>
+        <v>129472637</v>
       </c>
       <c r="B32" t="n">
-        <v>91573</v>
+        <v>57724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3619,33 +3619,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740756</v>
+        <v>740653</v>
       </c>
       <c r="R32" t="n">
-        <v>7126511</v>
+        <v>7126414</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3686,7 +3687,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472628</v>
+        <v>129472626</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741005</v>
+        <v>740672</v>
       </c>
       <c r="R33" t="n">
-        <v>7126520</v>
+        <v>7126349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472626</v>
+        <v>129472628</v>
       </c>
       <c r="B34" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>740672</v>
+        <v>741005</v>
       </c>
       <c r="R34" t="n">
-        <v>7126349</v>
+        <v>7126520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3996,53 +3996,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472656</v>
+        <v>129472620</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>740916</v>
+        <v>741005</v>
       </c>
       <c r="R36" t="n">
-        <v>7126531</v>
+        <v>7126496</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4083,7 +4075,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4102,45 +4093,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472665</v>
+        <v>129472656</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740726</v>
+        <v>740916</v>
       </c>
       <c r="R37" t="n">
-        <v>7126418</v>
+        <v>7126531</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,6 +4180,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4199,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472620</v>
+        <v>129472665</v>
       </c>
       <c r="B38" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741005</v>
+        <v>740726</v>
       </c>
       <c r="R38" t="n">
-        <v>7126496</v>
+        <v>7126418</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472641</v>
+        <v>129472630</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740707</v>
+        <v>740934</v>
       </c>
       <c r="R41" t="n">
-        <v>7126416</v>
+        <v>7126499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4561,11 +4561,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4689,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472630</v>
+        <v>129472641</v>
       </c>
       <c r="B43" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4724,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740934</v>
+        <v>740707</v>
       </c>
       <c r="R43" t="n">
-        <v>7126499</v>
+        <v>7126416</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4760,6 +4755,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472667</v>
+        <v>129472638</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740732</v>
+        <v>740703</v>
       </c>
       <c r="R44" t="n">
-        <v>7126394</v>
+        <v>7126419</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472638</v>
+        <v>129472667</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5185,21 +5185,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740703</v>
+        <v>740732</v>
       </c>
       <c r="R48" t="n">
-        <v>7126419</v>
+        <v>7126394</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472623</v>
+        <v>129472650</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>740728</v>
+        <v>740934</v>
       </c>
       <c r="R50" t="n">
-        <v>7126370</v>
+        <v>7126495</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472650</v>
+        <v>129472623</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>740934</v>
+        <v>740728</v>
       </c>
       <c r="R51" t="n">
-        <v>7126495</v>
+        <v>7126370</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -2901,7 +2901,7 @@
         <v>129472639</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>129472644</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>129472669</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472658</v>
+        <v>129472636</v>
       </c>
       <c r="B28" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,19 +3222,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3242,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740964</v>
+        <v>740773</v>
       </c>
       <c r="R28" t="n">
-        <v>7126508</v>
+        <v>7126518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472659</v>
+        <v>129472637</v>
       </c>
       <c r="B29" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3315,33 +3319,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740756</v>
+        <v>740653</v>
       </c>
       <c r="R29" t="n">
-        <v>7126511</v>
+        <v>7126414</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3382,7 +3387,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3404,7 +3408,7 @@
         <v>129472668</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3511,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472636</v>
+        <v>129472658</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>91601</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3522,23 +3526,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740773</v>
+        <v>740964</v>
       </c>
       <c r="R31" t="n">
-        <v>7126518</v>
+        <v>7126508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472637</v>
+        <v>129472659</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>91601</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3619,34 +3619,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740653</v>
+        <v>740756</v>
       </c>
       <c r="R32" t="n">
-        <v>7126414</v>
+        <v>7126511</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,6 +3686,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>129472626</v>
       </c>
       <c r="B33" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>129472628</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>97604</v>
+        <v>97633</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,32 +3996,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472620</v>
+        <v>129472665</v>
       </c>
       <c r="B36" t="n">
-        <v>91517</v>
+        <v>79070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741005</v>
+        <v>740726</v>
       </c>
       <c r="R36" t="n">
-        <v>7126496</v>
+        <v>7126418</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4093,53 +4093,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472656</v>
+        <v>129472620</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>91545</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740916</v>
+        <v>741005</v>
       </c>
       <c r="R37" t="n">
-        <v>7126531</v>
+        <v>7126496</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4180,7 +4172,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4199,10 +4190,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472665</v>
+        <v>129472634</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4210,21 +4201,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4225,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>740726</v>
+        <v>740970</v>
       </c>
       <c r="R38" t="n">
-        <v>7126418</v>
+        <v>7126500</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4296,45 +4287,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472634</v>
+        <v>129472656</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>98756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740970</v>
+        <v>740916</v>
       </c>
       <c r="R39" t="n">
-        <v>7126500</v>
+        <v>7126531</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4375,6 +4374,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>129472624</v>
       </c>
       <c r="B40" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>129472630</v>
       </c>
       <c r="B41" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>129472664</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>129472641</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>129472638</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>129472651</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>129472629</v>
       </c>
       <c r="B46" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>129472631</v>
       </c>
       <c r="B47" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>129472667</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>129472643</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>129472650</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>129472623</v>
       </c>
       <c r="B51" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>129472635</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>129472642</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>129472649</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>129457856</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>129460734</v>
       </c>
       <c r="B56" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>129472622</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>129472652</v>
       </c>
       <c r="B58" t="n">
-        <v>80185</v>
+        <v>80211</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>129472640</v>
       </c>
       <c r="B59" t="n">
-        <v>83010</v>
+        <v>83037</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472636</v>
+        <v>129472658</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>91601</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,23 +3222,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3246,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740773</v>
+        <v>740964</v>
       </c>
       <c r="R28" t="n">
-        <v>7126518</v>
+        <v>7126508</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3304,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472637</v>
+        <v>129472659</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>91601</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,34 +3315,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740653</v>
+        <v>740756</v>
       </c>
       <c r="R29" t="n">
-        <v>7126414</v>
+        <v>7126511</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3387,6 +3382,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3405,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472668</v>
+        <v>129472636</v>
       </c>
       <c r="B30" t="n">
-        <v>57730</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,16 +3412,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3434,24 +3430,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740760</v>
+        <v>740773</v>
       </c>
       <c r="R30" t="n">
-        <v>7126375</v>
+        <v>7126518</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3484,11 +3472,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3515,10 +3498,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472658</v>
+        <v>129472637</v>
       </c>
       <c r="B31" t="n">
-        <v>91601</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,19 +3509,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3546,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740964</v>
+        <v>740653</v>
       </c>
       <c r="R31" t="n">
-        <v>7126508</v>
+        <v>7126414</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3608,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472659</v>
+        <v>129472668</v>
       </c>
       <c r="B32" t="n">
-        <v>91601</v>
+        <v>57730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3619,22 +3606,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3642,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740756</v>
+        <v>740760</v>
       </c>
       <c r="R32" t="n">
-        <v>7126511</v>
+        <v>7126375</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3680,13 +3676,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472638</v>
+        <v>129472651</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740703</v>
+        <v>740934</v>
       </c>
       <c r="R44" t="n">
-        <v>7126419</v>
+        <v>7126501</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,32 +4883,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472651</v>
+        <v>129472629</v>
       </c>
       <c r="B45" t="n">
-        <v>80175</v>
+        <v>80204</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740934</v>
+        <v>740940</v>
       </c>
       <c r="R45" t="n">
-        <v>7126501</v>
+        <v>7126498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129472629</v>
+        <v>129472631</v>
       </c>
       <c r="B46" t="n">
         <v>80204</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>740940</v>
+        <v>740934</v>
       </c>
       <c r="R46" t="n">
-        <v>7126498</v>
+        <v>7126501</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5077,32 +5077,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472631</v>
+        <v>129472667</v>
       </c>
       <c r="B47" t="n">
-        <v>80204</v>
+        <v>79070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740934</v>
+        <v>740732</v>
       </c>
       <c r="R47" t="n">
-        <v>7126501</v>
+        <v>7126394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472667</v>
+        <v>129472638</v>
       </c>
       <c r="B48" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5185,21 +5185,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740732</v>
+        <v>740703</v>
       </c>
       <c r="R48" t="n">
-        <v>7126394</v>
+        <v>7126419</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5867,49 +5867,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129457856</v>
+        <v>129460734</v>
       </c>
       <c r="B55" t="n">
-        <v>57890</v>
+        <v>98756</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>740471</v>
+        <v>740827</v>
       </c>
       <c r="R55" t="n">
-        <v>7126406</v>
+        <v>7126414</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5968,54 +5973,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129460734</v>
+        <v>129457856</v>
       </c>
       <c r="B56" t="n">
-        <v>98756</v>
+        <v>57890</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>740827</v>
+        <v>740471</v>
       </c>
       <c r="R56" t="n">
-        <v>7126414</v>
+        <v>7126406</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -2901,7 +2901,7 @@
         <v>129472639</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>129472644</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>129472669</v>
       </c>
       <c r="B27" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>129472658</v>
       </c>
       <c r="B28" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>129472659</v>
       </c>
       <c r="B29" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472636</v>
+        <v>129472668</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3430,16 +3430,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740773</v>
+        <v>740760</v>
       </c>
       <c r="R30" t="n">
-        <v>7126518</v>
+        <v>7126375</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3472,6 +3480,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3501,7 +3514,7 @@
         <v>129472637</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3595,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472668</v>
+        <v>129472636</v>
       </c>
       <c r="B32" t="n">
-        <v>57730</v>
+        <v>57732</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,16 +3619,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3624,24 +3637,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740760</v>
+        <v>740773</v>
       </c>
       <c r="R32" t="n">
-        <v>7126375</v>
+        <v>7126518</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3674,11 +3679,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3708,7 +3708,7 @@
         <v>129472626</v>
       </c>
       <c r="B33" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>129472628</v>
       </c>
       <c r="B34" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>97633</v>
+        <v>97645</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472665</v>
+        <v>129472634</v>
       </c>
       <c r="B36" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4007,21 +4007,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>740726</v>
+        <v>740970</v>
       </c>
       <c r="R36" t="n">
-        <v>7126418</v>
+        <v>7126500</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4093,45 +4093,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472620</v>
+        <v>129472656</v>
       </c>
       <c r="B37" t="n">
-        <v>91545</v>
+        <v>98768</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>741005</v>
+        <v>740916</v>
       </c>
       <c r="R37" t="n">
-        <v>7126496</v>
+        <v>7126531</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4172,6 +4180,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4190,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472634</v>
+        <v>129472620</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>91551</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4225,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>740970</v>
+        <v>741005</v>
       </c>
       <c r="R38" t="n">
-        <v>7126500</v>
+        <v>7126496</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4287,53 +4296,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472656</v>
+        <v>129472665</v>
       </c>
       <c r="B39" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740916</v>
+        <v>740726</v>
       </c>
       <c r="R39" t="n">
-        <v>7126531</v>
+        <v>7126418</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4374,7 +4375,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>129472624</v>
       </c>
       <c r="B40" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472630</v>
+        <v>129472664</v>
       </c>
       <c r="B41" t="n">
-        <v>80204</v>
+        <v>79075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740934</v>
+        <v>740964</v>
       </c>
       <c r="R41" t="n">
-        <v>7126499</v>
+        <v>7126507</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472664</v>
+        <v>129472641</v>
       </c>
       <c r="B42" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740964</v>
+        <v>740707</v>
       </c>
       <c r="R42" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4658,6 +4658,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4684,32 +4689,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472641</v>
+        <v>129472630</v>
       </c>
       <c r="B43" t="n">
-        <v>57730</v>
+        <v>80209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4724,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740707</v>
+        <v>740934</v>
       </c>
       <c r="R43" t="n">
-        <v>7126416</v>
+        <v>7126499</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4755,11 +4760,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4789,7 +4789,7 @@
         <v>129472651</v>
       </c>
       <c r="B44" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>129472629</v>
       </c>
       <c r="B45" t="n">
-        <v>80204</v>
+        <v>80209</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>129472631</v>
       </c>
       <c r="B46" t="n">
-        <v>80204</v>
+        <v>80209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5077,10 +5077,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472667</v>
+        <v>129472643</v>
       </c>
       <c r="B47" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5088,21 +5088,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740732</v>
+        <v>740770</v>
       </c>
       <c r="R47" t="n">
-        <v>7126394</v>
+        <v>7126390</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5148,6 +5148,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5174,10 +5179,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472638</v>
+        <v>129472667</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5185,21 +5190,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5214,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740703</v>
+        <v>740732</v>
       </c>
       <c r="R48" t="n">
-        <v>7126419</v>
+        <v>7126394</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5271,10 +5276,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472643</v>
+        <v>129472638</v>
       </c>
       <c r="B49" t="n">
-        <v>57730</v>
+        <v>57732</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5282,16 +5287,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5306,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>740770</v>
+        <v>740703</v>
       </c>
       <c r="R49" t="n">
-        <v>7126390</v>
+        <v>7126419</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5342,11 +5347,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472650</v>
+        <v>129472623</v>
       </c>
       <c r="B50" t="n">
-        <v>80175</v>
+        <v>91587</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>740934</v>
+        <v>740728</v>
       </c>
       <c r="R50" t="n">
-        <v>7126495</v>
+        <v>7126370</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472623</v>
+        <v>129472650</v>
       </c>
       <c r="B51" t="n">
-        <v>91581</v>
+        <v>80180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>740728</v>
+        <v>740934</v>
       </c>
       <c r="R51" t="n">
-        <v>7126370</v>
+        <v>7126495</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5570,7 +5570,7 @@
         <v>129472635</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>129472642</v>
       </c>
       <c r="B53" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>129472649</v>
       </c>
       <c r="B54" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5867,54 +5867,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129460734</v>
+        <v>129457856</v>
       </c>
       <c r="B55" t="n">
-        <v>98756</v>
+        <v>57895</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>740827</v>
+        <v>740471</v>
       </c>
       <c r="R55" t="n">
-        <v>7126414</v>
+        <v>7126406</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5973,49 +5968,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129457856</v>
+        <v>129460734</v>
       </c>
       <c r="B56" t="n">
-        <v>57890</v>
+        <v>98768</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>740471</v>
+        <v>740827</v>
       </c>
       <c r="R56" t="n">
-        <v>7126406</v>
+        <v>7126414</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6077,7 +6077,7 @@
         <v>129472622</v>
       </c>
       <c r="B57" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>129472652</v>
       </c>
       <c r="B58" t="n">
-        <v>80211</v>
+        <v>80216</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>129472640</v>
       </c>
       <c r="B59" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -2901,7 +2901,7 @@
         <v>129472639</v>
       </c>
       <c r="B25" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>129472644</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>129472669</v>
       </c>
       <c r="B27" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>129472658</v>
       </c>
       <c r="B28" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>129472659</v>
       </c>
       <c r="B29" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472668</v>
+        <v>129472636</v>
       </c>
       <c r="B30" t="n">
-        <v>57735</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3430,24 +3430,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740760</v>
+        <v>740773</v>
       </c>
       <c r="R30" t="n">
-        <v>7126375</v>
+        <v>7126518</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3480,11 +3472,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3514,7 +3501,7 @@
         <v>129472637</v>
       </c>
       <c r="B31" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3608,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472636</v>
+        <v>129472668</v>
       </c>
       <c r="B32" t="n">
-        <v>57732</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3619,16 +3606,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3637,16 +3624,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740773</v>
+        <v>740760</v>
       </c>
       <c r="R32" t="n">
-        <v>7126518</v>
+        <v>7126375</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3679,6 +3674,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3708,7 +3708,7 @@
         <v>129472626</v>
       </c>
       <c r="B33" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>129472628</v>
       </c>
       <c r="B34" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>97645</v>
+        <v>97646</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>129472634</v>
       </c>
       <c r="B36" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4093,53 +4093,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472656</v>
+        <v>129472620</v>
       </c>
       <c r="B37" t="n">
-        <v>98768</v>
+        <v>91552</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740916</v>
+        <v>741005</v>
       </c>
       <c r="R37" t="n">
-        <v>7126531</v>
+        <v>7126496</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4180,7 +4172,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4199,32 +4190,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472620</v>
+        <v>129472665</v>
       </c>
       <c r="B38" t="n">
-        <v>91551</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4225,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741005</v>
+        <v>740726</v>
       </c>
       <c r="R38" t="n">
-        <v>7126496</v>
+        <v>7126418</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4296,45 +4287,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472665</v>
+        <v>129472656</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740726</v>
+        <v>740916</v>
       </c>
       <c r="R39" t="n">
-        <v>7126418</v>
+        <v>7126531</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4375,6 +4374,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>129472624</v>
       </c>
       <c r="B40" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>129472664</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472641</v>
+        <v>129472630</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>80210</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740707</v>
+        <v>740934</v>
       </c>
       <c r="R42" t="n">
-        <v>7126416</v>
+        <v>7126499</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4658,11 +4658,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4689,32 +4684,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472630</v>
+        <v>129472641</v>
       </c>
       <c r="B43" t="n">
-        <v>80209</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4724,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740934</v>
+        <v>740707</v>
       </c>
       <c r="R43" t="n">
-        <v>7126499</v>
+        <v>7126416</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4760,6 +4755,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472651</v>
+        <v>129472643</v>
       </c>
       <c r="B44" t="n">
-        <v>80180</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740934</v>
+        <v>740770</v>
       </c>
       <c r="R44" t="n">
-        <v>7126501</v>
+        <v>7126390</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4857,6 +4857,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4883,32 +4888,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472629</v>
+        <v>129472667</v>
       </c>
       <c r="B45" t="n">
-        <v>80209</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4923,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740940</v>
+        <v>740732</v>
       </c>
       <c r="R45" t="n">
-        <v>7126498</v>
+        <v>7126394</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,32 +4985,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129472631</v>
+        <v>129472638</v>
       </c>
       <c r="B46" t="n">
-        <v>80209</v>
+        <v>57733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5015,10 +5020,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>740934</v>
+        <v>740703</v>
       </c>
       <c r="R46" t="n">
-        <v>7126501</v>
+        <v>7126419</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5077,10 +5082,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472643</v>
+        <v>129472651</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5088,21 +5093,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5112,10 +5117,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740770</v>
+        <v>740934</v>
       </c>
       <c r="R47" t="n">
-        <v>7126390</v>
+        <v>7126501</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5148,11 +5153,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5179,32 +5179,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472667</v>
+        <v>129472629</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>80210</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740732</v>
+        <v>740940</v>
       </c>
       <c r="R48" t="n">
-        <v>7126394</v>
+        <v>7126498</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472638</v>
+        <v>129472631</v>
       </c>
       <c r="B49" t="n">
-        <v>57732</v>
+        <v>80210</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>740703</v>
+        <v>740934</v>
       </c>
       <c r="R49" t="n">
-        <v>7126419</v>
+        <v>7126501</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
         <v>129472623</v>
       </c>
       <c r="B50" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>129472650</v>
       </c>
       <c r="B51" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5567,10 +5567,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129472635</v>
+        <v>129472642</v>
       </c>
       <c r="B52" t="n">
-        <v>57732</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5578,16 +5578,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5596,16 +5596,20 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>740929</v>
+        <v>740685</v>
       </c>
       <c r="R52" t="n">
-        <v>7126517</v>
+        <v>7126341</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5638,6 +5642,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5664,10 +5673,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129472642</v>
+        <v>129472635</v>
       </c>
       <c r="B53" t="n">
-        <v>57735</v>
+        <v>57733</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5675,16 +5684,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5693,20 +5702,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>740685</v>
+        <v>740929</v>
       </c>
       <c r="R53" t="n">
-        <v>7126341</v>
+        <v>7126517</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5739,11 +5744,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5773,7 +5773,7 @@
         <v>129472649</v>
       </c>
       <c r="B54" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5867,49 +5867,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129457856</v>
+        <v>129460734</v>
       </c>
       <c r="B55" t="n">
-        <v>57895</v>
+        <v>98769</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>740471</v>
+        <v>740827</v>
       </c>
       <c r="R55" t="n">
-        <v>7126406</v>
+        <v>7126414</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5968,54 +5973,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129460734</v>
+        <v>129457856</v>
       </c>
       <c r="B56" t="n">
-        <v>98768</v>
+        <v>57896</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>740827</v>
+        <v>740471</v>
       </c>
       <c r="R56" t="n">
-        <v>7126414</v>
+        <v>7126406</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6077,7 +6077,7 @@
         <v>129472622</v>
       </c>
       <c r="B57" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>129472652</v>
       </c>
       <c r="B58" t="n">
-        <v>80216</v>
+        <v>80217</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>129472640</v>
       </c>
       <c r="B59" t="n">
-        <v>83042</v>
+        <v>83043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472658</v>
+        <v>129472636</v>
       </c>
       <c r="B28" t="n">
-        <v>91608</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,19 +3222,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3242,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740964</v>
+        <v>740773</v>
       </c>
       <c r="R28" t="n">
-        <v>7126508</v>
+        <v>7126518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472659</v>
+        <v>129472637</v>
       </c>
       <c r="B29" t="n">
-        <v>91608</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3315,33 +3319,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740756</v>
+        <v>740653</v>
       </c>
       <c r="R29" t="n">
-        <v>7126511</v>
+        <v>7126414</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3382,7 +3387,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3401,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472636</v>
+        <v>129472668</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,16 +3416,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3430,16 +3434,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740773</v>
+        <v>740760</v>
       </c>
       <c r="R30" t="n">
-        <v>7126518</v>
+        <v>7126375</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3472,6 +3484,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3498,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472637</v>
+        <v>129472658</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>91608</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3509,23 +3526,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3533,10 +3546,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740653</v>
+        <v>740964</v>
       </c>
       <c r="R31" t="n">
-        <v>7126414</v>
+        <v>7126508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3595,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472668</v>
+        <v>129472659</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>91608</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,31 +3619,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3638,10 +3642,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740760</v>
+        <v>740756</v>
       </c>
       <c r="R32" t="n">
-        <v>7126375</v>
+        <v>7126511</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3676,17 +3680,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472628</v>
+        <v>129472647</v>
       </c>
       <c r="B34" t="n">
-        <v>57896</v>
+        <v>97646</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741005</v>
+        <v>740823</v>
       </c>
       <c r="R34" t="n">
-        <v>7126520</v>
+        <v>7126527</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3899,32 +3899,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472647</v>
+        <v>129472628</v>
       </c>
       <c r="B35" t="n">
-        <v>97646</v>
+        <v>57896</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>740823</v>
+        <v>741005</v>
       </c>
       <c r="R35" t="n">
-        <v>7126527</v>
+        <v>7126520</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4093,45 +4093,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472620</v>
+        <v>129472656</v>
       </c>
       <c r="B37" t="n">
-        <v>91552</v>
+        <v>98769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>741005</v>
+        <v>740916</v>
       </c>
       <c r="R37" t="n">
-        <v>7126496</v>
+        <v>7126531</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4172,6 +4180,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4190,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472665</v>
+        <v>129472620</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>91552</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4225,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>740726</v>
+        <v>741005</v>
       </c>
       <c r="R38" t="n">
-        <v>7126418</v>
+        <v>7126496</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4287,53 +4296,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472656</v>
+        <v>129472665</v>
       </c>
       <c r="B39" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740916</v>
+        <v>740726</v>
       </c>
       <c r="R39" t="n">
-        <v>7126531</v>
+        <v>7126418</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4374,7 +4375,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472664</v>
+        <v>129472630</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>80210</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740964</v>
+        <v>740934</v>
       </c>
       <c r="R41" t="n">
-        <v>7126507</v>
+        <v>7126499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472630</v>
+        <v>129472664</v>
       </c>
       <c r="B42" t="n">
-        <v>80210</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740934</v>
+        <v>740964</v>
       </c>
       <c r="R42" t="n">
-        <v>7126499</v>
+        <v>7126507</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5867,54 +5867,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129460734</v>
+        <v>129457856</v>
       </c>
       <c r="B55" t="n">
-        <v>98769</v>
+        <v>57896</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>740827</v>
+        <v>740471</v>
       </c>
       <c r="R55" t="n">
-        <v>7126414</v>
+        <v>7126406</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5973,49 +5968,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129457856</v>
+        <v>129460734</v>
       </c>
       <c r="B56" t="n">
-        <v>57896</v>
+        <v>98769</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>740471</v>
+        <v>740827</v>
       </c>
       <c r="R56" t="n">
-        <v>7126406</v>
+        <v>7126414</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472636</v>
+        <v>129472658</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>91613</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,23 +3222,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3246,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740773</v>
+        <v>740964</v>
       </c>
       <c r="R28" t="n">
-        <v>7126518</v>
+        <v>7126508</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3304,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472637</v>
+        <v>129472659</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>91613</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,34 +3315,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740653</v>
+        <v>740756</v>
       </c>
       <c r="R29" t="n">
-        <v>7126414</v>
+        <v>7126511</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3387,6 +3382,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3405,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472668</v>
+        <v>129472636</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,16 +3412,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3434,24 +3430,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740760</v>
+        <v>740773</v>
       </c>
       <c r="R30" t="n">
-        <v>7126375</v>
+        <v>7126518</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3484,11 +3472,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3515,10 +3498,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472658</v>
+        <v>129472637</v>
       </c>
       <c r="B31" t="n">
-        <v>91608</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3526,19 +3509,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3546,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740964</v>
+        <v>740653</v>
       </c>
       <c r="R31" t="n">
-        <v>7126508</v>
+        <v>7126414</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3608,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472659</v>
+        <v>129472668</v>
       </c>
       <c r="B32" t="n">
-        <v>91608</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3619,22 +3606,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3642,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740756</v>
+        <v>740760</v>
       </c>
       <c r="R32" t="n">
-        <v>7126511</v>
+        <v>7126375</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3680,13 +3676,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472626</v>
+        <v>129472628</v>
       </c>
       <c r="B33" t="n">
-        <v>56926</v>
+        <v>57896</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>740672</v>
+        <v>741005</v>
       </c>
       <c r="R33" t="n">
-        <v>7126349</v>
+        <v>7126520</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472647</v>
+        <v>129472626</v>
       </c>
       <c r="B34" t="n">
-        <v>97646</v>
+        <v>56926</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>740823</v>
+        <v>740672</v>
       </c>
       <c r="R34" t="n">
-        <v>7126527</v>
+        <v>7126349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3899,32 +3899,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472628</v>
+        <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>57896</v>
+        <v>97651</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741005</v>
+        <v>740823</v>
       </c>
       <c r="R35" t="n">
-        <v>7126520</v>
+        <v>7126527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3996,32 +3996,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472634</v>
+        <v>129472620</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>91557</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>740970</v>
+        <v>741005</v>
       </c>
       <c r="R36" t="n">
-        <v>7126500</v>
+        <v>7126496</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4093,53 +4093,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472656</v>
+        <v>129472665</v>
       </c>
       <c r="B37" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740916</v>
+        <v>740726</v>
       </c>
       <c r="R37" t="n">
-        <v>7126531</v>
+        <v>7126418</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4180,7 +4172,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4199,32 +4190,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472620</v>
+        <v>129472634</v>
       </c>
       <c r="B38" t="n">
-        <v>91552</v>
+        <v>57733</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4234,10 +4225,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741005</v>
+        <v>740970</v>
       </c>
       <c r="R38" t="n">
-        <v>7126496</v>
+        <v>7126500</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4296,45 +4287,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472665</v>
+        <v>129472656</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740726</v>
+        <v>740916</v>
       </c>
       <c r="R39" t="n">
-        <v>7126418</v>
+        <v>7126531</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4375,6 +4374,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>129472624</v>
       </c>
       <c r="B40" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>129472630</v>
       </c>
       <c r="B41" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>129472664</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472643</v>
+        <v>129472651</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740770</v>
+        <v>740934</v>
       </c>
       <c r="R44" t="n">
-        <v>7126390</v>
+        <v>7126501</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4857,11 +4857,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4888,32 +4883,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472667</v>
+        <v>129472629</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>80215</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4923,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740732</v>
+        <v>740940</v>
       </c>
       <c r="R45" t="n">
-        <v>7126394</v>
+        <v>7126498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4985,32 +4980,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129472638</v>
+        <v>129472631</v>
       </c>
       <c r="B46" t="n">
-        <v>57733</v>
+        <v>80215</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5020,10 +5015,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>740703</v>
+        <v>740934</v>
       </c>
       <c r="R46" t="n">
-        <v>7126419</v>
+        <v>7126501</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5082,10 +5077,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472651</v>
+        <v>129472667</v>
       </c>
       <c r="B47" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5093,21 +5088,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5117,10 +5112,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740934</v>
+        <v>740732</v>
       </c>
       <c r="R47" t="n">
-        <v>7126501</v>
+        <v>7126394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5179,32 +5174,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472629</v>
+        <v>129472638</v>
       </c>
       <c r="B48" t="n">
-        <v>80210</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5214,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740940</v>
+        <v>740703</v>
       </c>
       <c r="R48" t="n">
-        <v>7126498</v>
+        <v>7126419</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5276,32 +5271,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472631</v>
+        <v>129472643</v>
       </c>
       <c r="B49" t="n">
-        <v>80210</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5306,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>740934</v>
+        <v>740770</v>
       </c>
       <c r="R49" t="n">
-        <v>7126501</v>
+        <v>7126390</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5347,6 +5342,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5376,7 +5376,7 @@
         <v>129472623</v>
       </c>
       <c r="B50" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>129472650</v>
       </c>
       <c r="B51" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5567,10 +5567,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129472642</v>
+        <v>129472635</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5578,16 +5578,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5596,20 +5596,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>740685</v>
+        <v>740929</v>
       </c>
       <c r="R52" t="n">
-        <v>7126341</v>
+        <v>7126517</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5642,11 +5638,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5673,10 +5664,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129472635</v>
+        <v>129472642</v>
       </c>
       <c r="B53" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5684,16 +5675,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5702,16 +5693,20 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>740929</v>
+        <v>740685</v>
       </c>
       <c r="R53" t="n">
-        <v>7126517</v>
+        <v>7126341</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5744,6 +5739,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5773,7 +5773,7 @@
         <v>129472649</v>
       </c>
       <c r="B54" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>129460734</v>
       </c>
       <c r="B56" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>129472622</v>
       </c>
       <c r="B57" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>129472652</v>
       </c>
       <c r="B58" t="n">
-        <v>80217</v>
+        <v>80222</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>129472640</v>
       </c>
       <c r="B59" t="n">
-        <v>83043</v>
+        <v>83048</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472658</v>
+        <v>129472636</v>
       </c>
       <c r="B28" t="n">
-        <v>91613</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,19 +3222,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3242,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740964</v>
+        <v>740773</v>
       </c>
       <c r="R28" t="n">
-        <v>7126508</v>
+        <v>7126518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472659</v>
+        <v>129472637</v>
       </c>
       <c r="B29" t="n">
-        <v>91613</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3315,33 +3319,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740756</v>
+        <v>740653</v>
       </c>
       <c r="R29" t="n">
-        <v>7126511</v>
+        <v>7126414</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3382,7 +3387,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3401,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472636</v>
+        <v>129472658</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>91613</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,23 +3416,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740773</v>
+        <v>740964</v>
       </c>
       <c r="R30" t="n">
-        <v>7126518</v>
+        <v>7126508</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,10 +3498,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472637</v>
+        <v>129472659</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>91613</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3509,34 +3509,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740653</v>
+        <v>740756</v>
       </c>
       <c r="R31" t="n">
-        <v>7126414</v>
+        <v>7126511</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3577,6 +3576,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472628</v>
+        <v>129472647</v>
       </c>
       <c r="B33" t="n">
-        <v>57896</v>
+        <v>97651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741005</v>
+        <v>740823</v>
       </c>
       <c r="R33" t="n">
-        <v>7126520</v>
+        <v>7126527</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3899,32 +3899,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472647</v>
+        <v>129472628</v>
       </c>
       <c r="B35" t="n">
-        <v>97651</v>
+        <v>57896</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>740823</v>
+        <v>741005</v>
       </c>
       <c r="R35" t="n">
-        <v>7126527</v>
+        <v>7126520</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472630</v>
+        <v>129472641</v>
       </c>
       <c r="B41" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740934</v>
+        <v>740707</v>
       </c>
       <c r="R41" t="n">
-        <v>7126499</v>
+        <v>7126416</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4561,6 +4561,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4684,32 +4689,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472641</v>
+        <v>129472630</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4724,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740707</v>
+        <v>740934</v>
       </c>
       <c r="R43" t="n">
-        <v>7126416</v>
+        <v>7126499</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4755,11 +4760,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4786,32 +4786,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472651</v>
+        <v>129472629</v>
       </c>
       <c r="B44" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740934</v>
+        <v>740940</v>
       </c>
       <c r="R44" t="n">
-        <v>7126501</v>
+        <v>7126498</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,32 +4883,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472629</v>
+        <v>129472651</v>
       </c>
       <c r="B45" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740940</v>
+        <v>740934</v>
       </c>
       <c r="R45" t="n">
-        <v>7126498</v>
+        <v>7126501</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5077,10 +5077,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472667</v>
+        <v>129472638</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5088,21 +5088,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740732</v>
+        <v>740703</v>
       </c>
       <c r="R47" t="n">
-        <v>7126394</v>
+        <v>7126419</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472638</v>
+        <v>129472667</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5185,21 +5185,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740703</v>
+        <v>740732</v>
       </c>
       <c r="R48" t="n">
-        <v>7126419</v>
+        <v>7126394</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472623</v>
+        <v>129472650</v>
       </c>
       <c r="B50" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>740728</v>
+        <v>740934</v>
       </c>
       <c r="R50" t="n">
-        <v>7126370</v>
+        <v>7126495</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472650</v>
+        <v>129472623</v>
       </c>
       <c r="B51" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>740934</v>
+        <v>740728</v>
       </c>
       <c r="R51" t="n">
-        <v>7126495</v>
+        <v>7126370</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472636</v>
+        <v>129472658</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>91613</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,23 +3222,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3246,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740773</v>
+        <v>740964</v>
       </c>
       <c r="R28" t="n">
-        <v>7126518</v>
+        <v>7126508</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3304,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472637</v>
+        <v>129472659</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>91613</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,34 +3315,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740653</v>
+        <v>740756</v>
       </c>
       <c r="R29" t="n">
-        <v>7126414</v>
+        <v>7126511</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3387,6 +3382,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3405,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472658</v>
+        <v>129472668</v>
       </c>
       <c r="B30" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,30 +3412,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740964</v>
+        <v>740760</v>
       </c>
       <c r="R30" t="n">
-        <v>7126508</v>
+        <v>7126375</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3472,6 +3480,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3498,10 +3511,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472659</v>
+        <v>129472636</v>
       </c>
       <c r="B31" t="n">
-        <v>91613</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3509,33 +3522,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740756</v>
+        <v>740773</v>
       </c>
       <c r="R31" t="n">
-        <v>7126511</v>
+        <v>7126518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3576,7 +3590,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3595,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472668</v>
+        <v>129472637</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,16 +3619,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3624,24 +3637,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740760</v>
+        <v>740653</v>
       </c>
       <c r="R32" t="n">
-        <v>7126375</v>
+        <v>7126414</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3674,11 +3679,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472647</v>
+        <v>129472626</v>
       </c>
       <c r="B33" t="n">
-        <v>97651</v>
+        <v>56926</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>740823</v>
+        <v>740672</v>
       </c>
       <c r="R33" t="n">
-        <v>7126527</v>
+        <v>7126349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472626</v>
+        <v>129472628</v>
       </c>
       <c r="B34" t="n">
-        <v>56926</v>
+        <v>57896</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>740672</v>
+        <v>741005</v>
       </c>
       <c r="R34" t="n">
-        <v>7126349</v>
+        <v>7126520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3899,32 +3899,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472628</v>
+        <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>57896</v>
+        <v>97651</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741005</v>
+        <v>740823</v>
       </c>
       <c r="R35" t="n">
-        <v>7126520</v>
+        <v>7126527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4093,45 +4093,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472665</v>
+        <v>129472656</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740726</v>
+        <v>740916</v>
       </c>
       <c r="R37" t="n">
-        <v>7126418</v>
+        <v>7126531</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4172,6 +4180,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4190,10 +4199,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472634</v>
+        <v>129472665</v>
       </c>
       <c r="B38" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4201,21 +4210,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4225,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>740970</v>
+        <v>740726</v>
       </c>
       <c r="R38" t="n">
-        <v>7126500</v>
+        <v>7126418</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4287,53 +4296,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472656</v>
+        <v>129472634</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740916</v>
+        <v>740970</v>
       </c>
       <c r="R39" t="n">
-        <v>7126531</v>
+        <v>7126500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4374,7 +4375,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4592,32 +4592,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472664</v>
+        <v>129472630</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740964</v>
+        <v>740934</v>
       </c>
       <c r="R42" t="n">
-        <v>7126507</v>
+        <v>7126499</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4689,32 +4689,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472630</v>
+        <v>129472664</v>
       </c>
       <c r="B43" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740934</v>
+        <v>740964</v>
       </c>
       <c r="R43" t="n">
-        <v>7126499</v>
+        <v>7126507</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4786,32 +4786,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472629</v>
+        <v>129472638</v>
       </c>
       <c r="B44" t="n">
-        <v>80215</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740940</v>
+        <v>740703</v>
       </c>
       <c r="R44" t="n">
-        <v>7126498</v>
+        <v>7126419</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472651</v>
+        <v>129472643</v>
       </c>
       <c r="B45" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740934</v>
+        <v>740770</v>
       </c>
       <c r="R45" t="n">
-        <v>7126501</v>
+        <v>7126390</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4954,6 +4954,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4980,7 +4985,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129472631</v>
+        <v>129472629</v>
       </c>
       <c r="B46" t="n">
         <v>80215</v>
@@ -5015,10 +5020,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>740934</v>
+        <v>740940</v>
       </c>
       <c r="R46" t="n">
-        <v>7126501</v>
+        <v>7126498</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5077,10 +5082,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472638</v>
+        <v>129472651</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5088,21 +5093,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5112,10 +5117,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740703</v>
+        <v>740934</v>
       </c>
       <c r="R47" t="n">
-        <v>7126419</v>
+        <v>7126501</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5174,32 +5179,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472667</v>
+        <v>129472631</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5214,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740732</v>
+        <v>740934</v>
       </c>
       <c r="R48" t="n">
-        <v>7126394</v>
+        <v>7126501</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5271,10 +5276,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472643</v>
+        <v>129472667</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5282,21 +5287,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5306,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>740770</v>
+        <v>740732</v>
       </c>
       <c r="R49" t="n">
-        <v>7126390</v>
+        <v>7126394</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5342,11 +5347,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5373,10 +5373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472650</v>
+        <v>129472623</v>
       </c>
       <c r="B50" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5384,21 +5384,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>740934</v>
+        <v>740728</v>
       </c>
       <c r="R50" t="n">
-        <v>7126495</v>
+        <v>7126370</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472623</v>
+        <v>129472650</v>
       </c>
       <c r="B51" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>740728</v>
+        <v>740934</v>
       </c>
       <c r="R51" t="n">
-        <v>7126370</v>
+        <v>7126495</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5567,10 +5567,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129472635</v>
+        <v>129472642</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5578,16 +5578,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5596,16 +5596,20 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>740929</v>
+        <v>740685</v>
       </c>
       <c r="R52" t="n">
-        <v>7126517</v>
+        <v>7126341</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5638,6 +5642,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5664,10 +5673,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129472642</v>
+        <v>129472635</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5675,16 +5684,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5693,20 +5702,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>740685</v>
+        <v>740929</v>
       </c>
       <c r="R53" t="n">
-        <v>7126341</v>
+        <v>7126517</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5739,11 +5744,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3211,7 +3211,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472658</v>
+        <v>129472659</v>
       </c>
       <c r="B28" t="n">
         <v>91613</v>
@@ -3236,16 +3236,19 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740964</v>
+        <v>740756</v>
       </c>
       <c r="R28" t="n">
-        <v>7126508</v>
+        <v>7126511</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3286,6 +3289,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3304,7 +3308,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472659</v>
+        <v>129472658</v>
       </c>
       <c r="B29" t="n">
         <v>91613</v>
@@ -3329,19 +3333,16 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740756</v>
+        <v>740964</v>
       </c>
       <c r="R29" t="n">
-        <v>7126511</v>
+        <v>7126508</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3382,7 +3383,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472668</v>
+        <v>129472637</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3430,24 +3430,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740760</v>
+        <v>740653</v>
       </c>
       <c r="R30" t="n">
-        <v>7126375</v>
+        <v>7126414</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3480,11 +3472,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3608,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472637</v>
+        <v>129472668</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3619,16 +3606,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3637,16 +3624,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740653</v>
+        <v>740760</v>
       </c>
       <c r="R32" t="n">
-        <v>7126414</v>
+        <v>7126375</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3679,6 +3674,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4093,53 +4093,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472656</v>
+        <v>129472634</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740916</v>
+        <v>740970</v>
       </c>
       <c r="R37" t="n">
-        <v>7126531</v>
+        <v>7126500</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4180,7 +4172,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4296,45 +4287,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472634</v>
+        <v>129472656</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740970</v>
+        <v>740916</v>
       </c>
       <c r="R39" t="n">
-        <v>7126500</v>
+        <v>7126531</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4375,6 +4374,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472641</v>
+        <v>129472630</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740707</v>
+        <v>740934</v>
       </c>
       <c r="R41" t="n">
-        <v>7126416</v>
+        <v>7126499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4561,11 +4561,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4592,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472630</v>
+        <v>129472664</v>
       </c>
       <c r="B42" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4627,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740934</v>
+        <v>740964</v>
       </c>
       <c r="R42" t="n">
-        <v>7126499</v>
+        <v>7126507</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4689,10 +4684,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472664</v>
+        <v>129472641</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4700,21 +4695,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4724,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740964</v>
+        <v>740707</v>
       </c>
       <c r="R43" t="n">
-        <v>7126507</v>
+        <v>7126416</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4760,6 +4755,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472638</v>
+        <v>129472667</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740703</v>
+        <v>740732</v>
       </c>
       <c r="R44" t="n">
-        <v>7126419</v>
+        <v>7126394</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472643</v>
+        <v>129472651</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740770</v>
+        <v>740934</v>
       </c>
       <c r="R45" t="n">
-        <v>7126390</v>
+        <v>7126501</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4954,11 +4954,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5082,32 +5077,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472651</v>
+        <v>129472631</v>
       </c>
       <c r="B47" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5179,32 +5174,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472631</v>
+        <v>129472643</v>
       </c>
       <c r="B48" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5214,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740934</v>
+        <v>740770</v>
       </c>
       <c r="R48" t="n">
-        <v>7126501</v>
+        <v>7126390</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5250,6 +5245,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472667</v>
+        <v>129472638</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>740732</v>
+        <v>740703</v>
       </c>
       <c r="R49" t="n">
-        <v>7126394</v>
+        <v>7126419</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472659</v>
+        <v>129472636</v>
       </c>
       <c r="B28" t="n">
-        <v>91613</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,33 +3222,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>740756</v>
+        <v>740773</v>
       </c>
       <c r="R28" t="n">
-        <v>7126511</v>
+        <v>7126518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3289,7 +3290,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472658</v>
+        <v>129472637</v>
       </c>
       <c r="B29" t="n">
-        <v>91613</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,19 +3319,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3339,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740964</v>
+        <v>740653</v>
       </c>
       <c r="R29" t="n">
-        <v>7126508</v>
+        <v>7126414</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3401,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472637</v>
+        <v>129472668</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,16 +3416,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3430,16 +3434,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740653</v>
+        <v>740760</v>
       </c>
       <c r="R30" t="n">
-        <v>7126414</v>
+        <v>7126375</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3472,6 +3484,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3498,10 +3515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472636</v>
+        <v>129472658</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>91617</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3509,23 +3526,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3533,10 +3546,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740773</v>
+        <v>740964</v>
       </c>
       <c r="R31" t="n">
-        <v>7126518</v>
+        <v>7126508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3595,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472668</v>
+        <v>129472659</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>91617</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,31 +3619,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3638,10 +3642,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740760</v>
+        <v>740756</v>
       </c>
       <c r="R32" t="n">
-        <v>7126375</v>
+        <v>7126511</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3676,17 +3680,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472626</v>
+        <v>129472628</v>
       </c>
       <c r="B33" t="n">
-        <v>56926</v>
+        <v>57896</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>740672</v>
+        <v>741005</v>
       </c>
       <c r="R33" t="n">
-        <v>7126349</v>
+        <v>7126520</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472628</v>
+        <v>129472626</v>
       </c>
       <c r="B34" t="n">
-        <v>57896</v>
+        <v>56926</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741005</v>
+        <v>740672</v>
       </c>
       <c r="R34" t="n">
-        <v>7126520</v>
+        <v>7126349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
         <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>97651</v>
+        <v>97655</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,32 +3996,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472620</v>
+        <v>129472634</v>
       </c>
       <c r="B36" t="n">
-        <v>91557</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741005</v>
+        <v>740970</v>
       </c>
       <c r="R36" t="n">
-        <v>7126496</v>
+        <v>7126500</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4093,32 +4093,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472634</v>
+        <v>129472620</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>91561</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>740970</v>
+        <v>741005</v>
       </c>
       <c r="R37" t="n">
-        <v>7126500</v>
+        <v>7126496</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4290,7 +4290,7 @@
         <v>129472656</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>129472624</v>
       </c>
       <c r="B40" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4490,32 +4490,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472630</v>
+        <v>129472664</v>
       </c>
       <c r="B41" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>740934</v>
+        <v>740964</v>
       </c>
       <c r="R41" t="n">
-        <v>7126499</v>
+        <v>7126507</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472664</v>
+        <v>129472630</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740964</v>
+        <v>740934</v>
       </c>
       <c r="R42" t="n">
-        <v>7126507</v>
+        <v>7126499</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472667</v>
+        <v>129472638</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740732</v>
+        <v>740703</v>
       </c>
       <c r="R44" t="n">
-        <v>7126394</v>
+        <v>7126419</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472643</v>
+        <v>129472667</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5185,21 +5185,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740770</v>
+        <v>740732</v>
       </c>
       <c r="R48" t="n">
-        <v>7126390</v>
+        <v>7126394</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5245,11 +5245,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5276,10 +5271,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472638</v>
+        <v>129472643</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5287,16 +5282,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5311,10 +5306,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>740703</v>
+        <v>740770</v>
       </c>
       <c r="R49" t="n">
-        <v>7126419</v>
+        <v>7126390</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5347,6 +5342,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5376,7 +5376,7 @@
         <v>129472623</v>
       </c>
       <c r="B50" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>129460734</v>
       </c>
       <c r="B56" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>129472622</v>
       </c>
       <c r="B57" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129472668</v>
+        <v>129472658</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,42 +3416,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>740760</v>
+        <v>740964</v>
       </c>
       <c r="R30" t="n">
-        <v>7126375</v>
+        <v>7126508</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3484,11 +3472,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färskt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3515,10 +3498,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472658</v>
+        <v>129472659</v>
       </c>
       <c r="B31" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3540,16 +3523,19 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>740964</v>
+        <v>740756</v>
       </c>
       <c r="R31" t="n">
-        <v>7126508</v>
+        <v>7126511</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,6 +3576,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3608,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472659</v>
+        <v>129472668</v>
       </c>
       <c r="B32" t="n">
-        <v>91617</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3619,22 +3606,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3642,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>740756</v>
+        <v>740760</v>
       </c>
       <c r="R32" t="n">
-        <v>7126511</v>
+        <v>7126375</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3680,13 +3676,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färskt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472628</v>
+        <v>129472647</v>
       </c>
       <c r="B33" t="n">
-        <v>57896</v>
+        <v>97657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741005</v>
+        <v>740823</v>
       </c>
       <c r="R33" t="n">
-        <v>7126520</v>
+        <v>7126527</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3899,32 +3899,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472647</v>
+        <v>129472628</v>
       </c>
       <c r="B35" t="n">
-        <v>97655</v>
+        <v>57896</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>740823</v>
+        <v>741005</v>
       </c>
       <c r="R35" t="n">
-        <v>7126527</v>
+        <v>7126520</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3996,45 +3996,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472634</v>
+        <v>129472656</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>740970</v>
+        <v>740916</v>
       </c>
       <c r="R36" t="n">
-        <v>7126500</v>
+        <v>7126531</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4075,6 +4083,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4093,32 +4102,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472620</v>
+        <v>129472665</v>
       </c>
       <c r="B37" t="n">
-        <v>91561</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4128,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>741005</v>
+        <v>740726</v>
       </c>
       <c r="R37" t="n">
-        <v>7126496</v>
+        <v>7126418</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4190,32 +4199,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129472665</v>
+        <v>129472620</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>91563</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4225,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>740726</v>
+        <v>741005</v>
       </c>
       <c r="R38" t="n">
-        <v>7126418</v>
+        <v>7126496</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4287,53 +4296,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472656</v>
+        <v>129472634</v>
       </c>
       <c r="B39" t="n">
-        <v>98778</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>740916</v>
+        <v>740970</v>
       </c>
       <c r="R39" t="n">
-        <v>7126531</v>
+        <v>7126500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4374,7 +4375,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>129472624</v>
       </c>
       <c r="B40" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472630</v>
+        <v>129472641</v>
       </c>
       <c r="B42" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>740934</v>
+        <v>740707</v>
       </c>
       <c r="R42" t="n">
-        <v>7126499</v>
+        <v>7126416</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4658,6 +4658,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4684,32 +4689,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472641</v>
+        <v>129472630</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4719,10 +4724,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>740707</v>
+        <v>740934</v>
       </c>
       <c r="R43" t="n">
-        <v>7126416</v>
+        <v>7126499</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4755,11 +4760,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129472638</v>
+        <v>129472667</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>740703</v>
+        <v>740732</v>
       </c>
       <c r="R44" t="n">
-        <v>7126419</v>
+        <v>7126394</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129472651</v>
+        <v>129472638</v>
       </c>
       <c r="B45" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>740934</v>
+        <v>740703</v>
       </c>
       <c r="R45" t="n">
-        <v>7126501</v>
+        <v>7126419</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,32 +4980,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129472629</v>
+        <v>129472651</v>
       </c>
       <c r="B46" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>740940</v>
+        <v>740934</v>
       </c>
       <c r="R46" t="n">
-        <v>7126498</v>
+        <v>7126501</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129472631</v>
+        <v>129472629</v>
       </c>
       <c r="B47" t="n">
         <v>80215</v>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>740934</v>
+        <v>740940</v>
       </c>
       <c r="R47" t="n">
-        <v>7126501</v>
+        <v>7126498</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5174,32 +5174,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472667</v>
+        <v>129472631</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>740732</v>
+        <v>740934</v>
       </c>
       <c r="R48" t="n">
-        <v>7126394</v>
+        <v>7126501</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
         <v>129472623</v>
       </c>
       <c r="B50" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5867,49 +5867,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129457856</v>
+        <v>129460734</v>
       </c>
       <c r="B55" t="n">
-        <v>57896</v>
+        <v>98780</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>740471</v>
+        <v>740827</v>
       </c>
       <c r="R55" t="n">
-        <v>7126406</v>
+        <v>7126414</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5968,54 +5973,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129460734</v>
+        <v>129457856</v>
       </c>
       <c r="B56" t="n">
-        <v>98778</v>
+        <v>57896</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>740827</v>
+        <v>740471</v>
       </c>
       <c r="R56" t="n">
-        <v>7126414</v>
+        <v>7126406</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6077,7 +6077,7 @@
         <v>129472622</v>
       </c>
       <c r="B57" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>129472640</v>
       </c>
       <c r="B59" t="n">
-        <v>83048</v>
+        <v>83050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 42702-2025 artfynd.xlsx
+++ b/artfynd/A 42702-2025 artfynd.xlsx
@@ -3705,10 +3705,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472647</v>
+        <v>129472626</v>
       </c>
       <c r="B33" t="n">
-        <v>97657</v>
+        <v>56926</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>740823</v>
+        <v>740672</v>
       </c>
       <c r="R33" t="n">
-        <v>7126527</v>
+        <v>7126349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472626</v>
+        <v>129472628</v>
       </c>
       <c r="B34" t="n">
-        <v>56926</v>
+        <v>57896</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>740672</v>
+        <v>741005</v>
       </c>
       <c r="R34" t="n">
-        <v>7126349</v>
+        <v>7126520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3899,32 +3899,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472628</v>
+        <v>129472647</v>
       </c>
       <c r="B35" t="n">
-        <v>57896</v>
+        <v>97657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741005</v>
+        <v>740823</v>
       </c>
       <c r="R35" t="n">
-        <v>7126520</v>
+        <v>7126527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5867,54 +5867,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129460734</v>
+        <v>129457856</v>
       </c>
       <c r="B55" t="n">
-        <v>98780</v>
+        <v>57896</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
+          <t>Invedatjärnen, Invedatjärnen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>740827</v>
+        <v>740471</v>
       </c>
       <c r="R55" t="n">
-        <v>7126414</v>
+        <v>7126406</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -5973,49 +5968,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129457856</v>
+        <v>129460734</v>
       </c>
       <c r="B56" t="n">
-        <v>57896</v>
+        <v>98780</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Invedatjärnen, Invedatjärnen, Vb</t>
+          <t>Invedatjärnbäcken, Invedatjärnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>740471</v>
+        <v>740827</v>
       </c>
       <c r="R56" t="n">
-        <v>7126406</v>
+        <v>7126414</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
